--- a/research/traditional_assets/database/data/italy/italy_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/italy/italy_hospitals_healthcare_facilities.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.0868357761082095</v>
+        <v>0.08666157024554981</v>
       </c>
       <c r="C2">
-        <v>761.2072756772093</v>
+        <v>756.7563562890753</v>
       </c>
       <c r="D2">
-        <v>737.7072756772093</v>
+        <v>740.8523562890753</v>
       </c>
       <c r="E2">
-        <v>-259</v>
+        <v>-251.404</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>7.596</v>
       </c>
       <c r="G2">
         <v>23.5</v>
@@ -1451,28 +1451,28 @@
         <v>71.875</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.3820788</v>
       </c>
       <c r="N2">
-        <v>71.875</v>
+        <v>71.4929212</v>
       </c>
       <c r="O2">
-        <v>17.25</v>
+        <v>17.158301088</v>
       </c>
       <c r="P2">
-        <v>54.625</v>
+        <v>54.334620112</v>
       </c>
       <c r="Q2">
-        <v>82.125</v>
+        <v>81.834620112</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.0868357761082095</v>
+        <v>0.08715079822782809</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5692093022525495</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>188.1156452543297</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.08666157024554981</v>
+        <v>0.08648736438289009</v>
       </c>
       <c r="C3">
-        <v>756.7563562890753</v>
+        <v>752.3323686764171</v>
       </c>
       <c r="D3">
-        <v>740.8523562890753</v>
+        <v>744.0243686764171</v>
       </c>
       <c r="E3">
-        <v>-251.404</v>
+        <v>-243.808</v>
       </c>
       <c r="F3">
-        <v>7.596</v>
+        <v>15.192</v>
       </c>
       <c r="G3">
         <v>23.5</v>
@@ -1533,28 +1533,28 @@
         <v>71.875</v>
       </c>
       <c r="M3">
-        <v>0.3820788</v>
+        <v>0.7641576</v>
       </c>
       <c r="N3">
-        <v>71.4929212</v>
+        <v>71.1108424</v>
       </c>
       <c r="O3">
-        <v>17.158301088</v>
+        <v>17.066602176</v>
       </c>
       <c r="P3">
-        <v>54.334620112</v>
+        <v>54.04424022399999</v>
       </c>
       <c r="Q3">
-        <v>81.834620112</v>
+        <v>81.54424022399999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.08715079822782809</v>
+        <v>0.08747224937029602</v>
       </c>
       <c r="T3">
-        <v>0.5692093022525495</v>
+        <v>0.5736341982244324</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>188.1156452543297</v>
+        <v>94.05782262716487</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.08648736438289009</v>
+        <v>0.08631315852023039</v>
       </c>
       <c r="C4">
-        <v>752.3323686764171</v>
+        <v>747.9356602577042</v>
       </c>
       <c r="D4">
-        <v>744.0243686764171</v>
+        <v>747.2236602577042</v>
       </c>
       <c r="E4">
-        <v>-243.808</v>
+        <v>-236.212</v>
       </c>
       <c r="F4">
-        <v>15.192</v>
+        <v>22.788</v>
       </c>
       <c r="G4">
         <v>23.5</v>
@@ -1615,28 +1615,28 @@
         <v>71.875</v>
       </c>
       <c r="M4">
-        <v>0.7641576</v>
+        <v>1.1462364</v>
       </c>
       <c r="N4">
-        <v>71.1108424</v>
+        <v>70.72876359999999</v>
       </c>
       <c r="O4">
-        <v>17.066602176</v>
+        <v>16.974903264</v>
       </c>
       <c r="P4">
-        <v>54.04424022399999</v>
+        <v>53.753860336</v>
       </c>
       <c r="Q4">
-        <v>81.54424022399999</v>
+        <v>81.253860336</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.08747224937029602</v>
+        <v>0.08780032837137154</v>
       </c>
       <c r="T4">
-        <v>0.5736341982244324</v>
+        <v>0.5781503291648078</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>94.05782262716487</v>
+        <v>62.70521508477657</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08631315852023039</v>
+        <v>0.08613895265757068</v>
       </c>
       <c r="C5">
-        <v>747.9356602577042</v>
+        <v>743.566584452785</v>
       </c>
       <c r="D5">
-        <v>747.2236602577042</v>
+        <v>750.4505844527851</v>
       </c>
       <c r="E5">
-        <v>-236.212</v>
+        <v>-228.616</v>
       </c>
       <c r="F5">
-        <v>22.788</v>
+        <v>30.384</v>
       </c>
       <c r="G5">
         <v>23.5</v>
@@ -1697,28 +1697,28 @@
         <v>71.875</v>
       </c>
       <c r="M5">
-        <v>1.1462364</v>
+        <v>1.5283152</v>
       </c>
       <c r="N5">
-        <v>70.72876359999999</v>
+        <v>70.34668480000001</v>
       </c>
       <c r="O5">
-        <v>16.974903264</v>
+        <v>16.883204352</v>
       </c>
       <c r="P5">
-        <v>53.753860336</v>
+        <v>53.46348044800001</v>
       </c>
       <c r="Q5">
-        <v>81.253860336</v>
+        <v>80.96348044800001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.08780032837137154</v>
+        <v>0.08813524235163614</v>
       </c>
       <c r="T5">
-        <v>0.5781503291648078</v>
+        <v>0.5827605461664409</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>62.70521508477657</v>
+        <v>47.02891131358244</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.08613895265757068</v>
+        <v>0.08596474679491098</v>
       </c>
       <c r="C6">
-        <v>743.566584452785</v>
+        <v>739.2255008130354</v>
       </c>
       <c r="D6">
-        <v>750.4505844527851</v>
+        <v>753.7055008130354</v>
       </c>
       <c r="E6">
-        <v>-228.616</v>
+        <v>-221.02</v>
       </c>
       <c r="F6">
-        <v>30.384</v>
+        <v>37.98</v>
       </c>
       <c r="G6">
         <v>23.5</v>
@@ -1779,28 +1779,28 @@
         <v>71.875</v>
       </c>
       <c r="M6">
-        <v>1.5283152</v>
+        <v>1.910394</v>
       </c>
       <c r="N6">
-        <v>70.34668480000001</v>
+        <v>69.964606</v>
       </c>
       <c r="O6">
-        <v>16.883204352</v>
+        <v>16.79150544</v>
       </c>
       <c r="P6">
-        <v>53.46348044800001</v>
+        <v>53.17310056</v>
       </c>
       <c r="Q6">
-        <v>80.96348044800001</v>
+        <v>80.67310055999999</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.08813524235163614</v>
+        <v>0.08847720715253789</v>
       </c>
       <c r="T6">
-        <v>0.5827605461664409</v>
+        <v>0.5874678203681085</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>47.02891131358244</v>
+        <v>37.62312905086595</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08596474679491098</v>
+        <v>0.08579054093225129</v>
       </c>
       <c r="C7">
-        <v>739.2255008130354</v>
+        <v>734.9127751549087</v>
       </c>
       <c r="D7">
-        <v>753.7055008130354</v>
+        <v>756.9887751549087</v>
       </c>
       <c r="E7">
-        <v>-221.02</v>
+        <v>-213.424</v>
       </c>
       <c r="F7">
-        <v>37.98</v>
+        <v>45.57600000000001</v>
       </c>
       <c r="G7">
         <v>23.5</v>
@@ -1861,28 +1861,28 @@
         <v>71.875</v>
       </c>
       <c r="M7">
-        <v>1.910394</v>
+        <v>2.2924728</v>
       </c>
       <c r="N7">
-        <v>69.964606</v>
+        <v>69.5825272</v>
       </c>
       <c r="O7">
-        <v>16.79150544</v>
+        <v>16.699806528</v>
       </c>
       <c r="P7">
-        <v>53.17310056</v>
+        <v>52.882720672</v>
       </c>
       <c r="Q7">
-        <v>80.67310055999999</v>
+        <v>80.382720672</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.08847720715253789</v>
+        <v>0.08882644780026733</v>
       </c>
       <c r="T7">
-        <v>0.5874678203681085</v>
+        <v>0.5922752493400243</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>37.62312905086595</v>
+        <v>31.35260754238829</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08579054093225129</v>
+        <v>0.0856163350695916</v>
       </c>
       <c r="C8">
-        <v>734.9127751549087</v>
+        <v>730.6287796969912</v>
       </c>
       <c r="D8">
-        <v>756.9887751549087</v>
+        <v>760.3007796969912</v>
       </c>
       <c r="E8">
-        <v>-213.424</v>
+        <v>-205.828</v>
       </c>
       <c r="F8">
-        <v>45.576</v>
+        <v>53.172</v>
       </c>
       <c r="G8">
         <v>23.5</v>
@@ -1943,28 +1943,28 @@
         <v>71.875</v>
       </c>
       <c r="M8">
-        <v>2.2924728</v>
+        <v>2.6745516</v>
       </c>
       <c r="N8">
-        <v>69.5825272</v>
+        <v>69.2004484</v>
       </c>
       <c r="O8">
-        <v>16.699806528</v>
+        <v>16.608107616</v>
       </c>
       <c r="P8">
-        <v>52.882720672</v>
+        <v>52.592340784</v>
       </c>
       <c r="Q8">
-        <v>80.382720672</v>
+        <v>80.092340784</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.08882644780026733</v>
+        <v>0.08918319899956084</v>
       </c>
       <c r="T8">
-        <v>0.5922752493400243</v>
+        <v>0.5971860638812285</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>31.35260754238829</v>
+        <v>26.87366360776139</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08561633506959158</v>
+        <v>0.08544212920693188</v>
       </c>
       <c r="C9">
-        <v>730.6287796969914</v>
+        <v>726.3738932006727</v>
       </c>
       <c r="D9">
-        <v>760.3007796969914</v>
+        <v>763.6418932006727</v>
       </c>
       <c r="E9">
-        <v>-205.828</v>
+        <v>-198.232</v>
       </c>
       <c r="F9">
-        <v>53.172</v>
+        <v>60.768</v>
       </c>
       <c r="G9">
         <v>23.5</v>
@@ -2025,28 +2025,28 @@
         <v>71.875</v>
       </c>
       <c r="M9">
-        <v>2.6745516</v>
+        <v>3.0566304</v>
       </c>
       <c r="N9">
-        <v>69.2004484</v>
+        <v>68.8183696</v>
       </c>
       <c r="O9">
-        <v>16.608107616</v>
+        <v>16.516408704</v>
       </c>
       <c r="P9">
-        <v>52.592340784</v>
+        <v>52.301960896</v>
       </c>
       <c r="Q9">
-        <v>80.092340784</v>
+        <v>79.801960896</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.08918319899956084</v>
+        <v>0.08954770565970856</v>
       </c>
       <c r="T9">
-        <v>0.5971860638812285</v>
+        <v>0.602203635260285</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>26.87366360776139</v>
+        <v>23.51445565679122</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08544212920693188</v>
+        <v>0.08526792334427218</v>
       </c>
       <c r="C10">
-        <v>726.3738932006727</v>
+        <v>722.14850111454</v>
       </c>
       <c r="D10">
-        <v>763.6418932006727</v>
+        <v>767.01250111454</v>
       </c>
       <c r="E10">
-        <v>-198.232</v>
+        <v>-190.636</v>
       </c>
       <c r="F10">
-        <v>60.768</v>
+        <v>68.364</v>
       </c>
       <c r="G10">
         <v>23.5</v>
@@ -2107,28 +2107,28 @@
         <v>71.875</v>
       </c>
       <c r="M10">
-        <v>3.0566304</v>
+        <v>3.4387092</v>
       </c>
       <c r="N10">
-        <v>68.8183696</v>
+        <v>68.43629079999999</v>
       </c>
       <c r="O10">
-        <v>16.516408704</v>
+        <v>16.424709792</v>
       </c>
       <c r="P10">
-        <v>52.301960896</v>
+        <v>52.01158100799999</v>
       </c>
       <c r="Q10">
-        <v>79.801960896</v>
+        <v>79.51158100799999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.08954770565970856</v>
+        <v>0.08992022345524414</v>
       </c>
       <c r="T10">
-        <v>0.602203635260285</v>
+        <v>0.6073314829333868</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>23.51445565679122</v>
+        <v>20.90173836159219</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08526792334427218</v>
+        <v>0.08509371748161249</v>
       </c>
       <c r="C11">
-        <v>722.14850111454</v>
+        <v>717.9529957226146</v>
       </c>
       <c r="D11">
-        <v>767.01250111454</v>
+        <v>770.4129957226146</v>
       </c>
       <c r="E11">
-        <v>-190.636</v>
+        <v>-183.04</v>
       </c>
       <c r="F11">
-        <v>68.364</v>
+        <v>75.95999999999999</v>
       </c>
       <c r="G11">
         <v>23.5</v>
@@ -2189,28 +2189,28 @@
         <v>71.875</v>
       </c>
       <c r="M11">
-        <v>3.4387092</v>
+        <v>3.820787999999999</v>
       </c>
       <c r="N11">
-        <v>68.43629079999999</v>
+        <v>68.05421200000001</v>
       </c>
       <c r="O11">
-        <v>16.424709792</v>
+        <v>16.33301088</v>
       </c>
       <c r="P11">
-        <v>52.01158100799999</v>
+        <v>51.72120112</v>
       </c>
       <c r="Q11">
-        <v>79.51158100799999</v>
+        <v>79.22120112</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.08992022345524414</v>
+        <v>0.09030101942401386</v>
       </c>
       <c r="T11">
-        <v>0.6073314829333868</v>
+        <v>0.6125732827770021</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>20.90173836159219</v>
+        <v>18.81156452543298</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08509371748161249</v>
+        <v>0.08491951161895278</v>
       </c>
       <c r="C12">
-        <v>717.9529957226146</v>
+        <v>713.7877762965488</v>
       </c>
       <c r="D12">
-        <v>770.4129957226146</v>
+        <v>773.8437762965489</v>
       </c>
       <c r="E12">
-        <v>-183.04</v>
+        <v>-175.444</v>
       </c>
       <c r="F12">
-        <v>75.96000000000001</v>
+        <v>83.556</v>
       </c>
       <c r="G12">
         <v>23.5</v>
@@ -2271,28 +2271,28 @@
         <v>71.875</v>
       </c>
       <c r="M12">
-        <v>3.820788</v>
+        <v>4.2028668</v>
       </c>
       <c r="N12">
-        <v>68.05421200000001</v>
+        <v>67.6721332</v>
       </c>
       <c r="O12">
-        <v>16.33301088</v>
+        <v>16.241311968</v>
       </c>
       <c r="P12">
-        <v>51.72120112</v>
+        <v>51.430821232</v>
       </c>
       <c r="Q12">
-        <v>79.22120112</v>
+        <v>78.930821232</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09030101942401386</v>
+        <v>0.09069037260556492</v>
       </c>
       <c r="T12">
-        <v>0.6125732827770021</v>
+        <v>0.6179328758755298</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>18.81156452543297</v>
+        <v>17.10142229584816</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08491951161895278</v>
+        <v>0.08474530575629306</v>
       </c>
       <c r="C13">
-        <v>713.7877762965488</v>
+        <v>709.6532492519079</v>
       </c>
       <c r="D13">
-        <v>773.8437762965489</v>
+        <v>777.305249251908</v>
       </c>
       <c r="E13">
-        <v>-175.444</v>
+        <v>-167.848</v>
       </c>
       <c r="F13">
-        <v>83.556</v>
+        <v>91.152</v>
       </c>
       <c r="G13">
         <v>23.5</v>
@@ -2353,28 +2353,28 @@
         <v>71.875</v>
       </c>
       <c r="M13">
-        <v>4.2028668</v>
+        <v>4.5849456</v>
       </c>
       <c r="N13">
-        <v>67.6721332</v>
+        <v>67.2900544</v>
       </c>
       <c r="O13">
-        <v>16.241311968</v>
+        <v>16.149613056</v>
       </c>
       <c r="P13">
-        <v>51.430821232</v>
+        <v>51.140441344</v>
       </c>
       <c r="Q13">
-        <v>78.930821232</v>
+        <v>78.64044134400001</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09069037260556492</v>
+        <v>0.0910885747230603</v>
       </c>
       <c r="T13">
-        <v>0.6179328758755298</v>
+        <v>0.623414277908115</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>17.10142229584816</v>
+        <v>15.67630377119414</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.08474530575629306</v>
+        <v>0.08457109989363336</v>
       </c>
       <c r="C14">
-        <v>709.6532492519079</v>
+        <v>705.5498283086624</v>
       </c>
       <c r="D14">
-        <v>777.305249251908</v>
+        <v>780.7978283086625</v>
       </c>
       <c r="E14">
-        <v>-167.848</v>
+        <v>-160.252</v>
       </c>
       <c r="F14">
-        <v>91.152</v>
+        <v>98.748</v>
       </c>
       <c r="G14">
         <v>23.5</v>
@@ -2435,28 +2435,28 @@
         <v>71.875</v>
       </c>
       <c r="M14">
-        <v>4.5849456</v>
+        <v>4.9670244</v>
       </c>
       <c r="N14">
-        <v>67.2900544</v>
+        <v>66.9079756</v>
       </c>
       <c r="O14">
-        <v>16.149613056</v>
+        <v>16.057914144</v>
       </c>
       <c r="P14">
-        <v>51.140441344</v>
+        <v>50.85006145600001</v>
       </c>
       <c r="Q14">
-        <v>78.64044134400001</v>
+        <v>78.35006145600001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0910885747230603</v>
+        <v>0.09149593091222226</v>
       </c>
       <c r="T14">
-        <v>0.623414277908115</v>
+        <v>0.6290216891828287</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>15.67630377119414</v>
+        <v>14.47043425033306</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.08457109989363336</v>
+        <v>0.08439689403097367</v>
       </c>
       <c r="C15">
-        <v>705.5498283086624</v>
+        <v>701.4779346560325</v>
       </c>
       <c r="D15">
-        <v>780.7978283086625</v>
+        <v>784.3219346560326</v>
       </c>
       <c r="E15">
-        <v>-160.252</v>
+        <v>-152.656</v>
       </c>
       <c r="F15">
-        <v>98.748</v>
+        <v>106.344</v>
       </c>
       <c r="G15">
         <v>23.5</v>
@@ -2517,28 +2517,28 @@
         <v>71.875</v>
       </c>
       <c r="M15">
-        <v>4.9670244</v>
+        <v>5.3491032</v>
       </c>
       <c r="N15">
-        <v>66.9079756</v>
+        <v>66.5258968</v>
       </c>
       <c r="O15">
-        <v>16.057914144</v>
+        <v>15.966215232</v>
       </c>
       <c r="P15">
-        <v>50.85006145600001</v>
+        <v>50.559681568</v>
       </c>
       <c r="Q15">
-        <v>78.35006145600001</v>
+        <v>78.059681568</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09149593091222226</v>
+        <v>0.09191276050113217</v>
       </c>
       <c r="T15">
-        <v>0.6290216891828287</v>
+        <v>0.6347595053709079</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>14.47043425033306</v>
+        <v>13.4368318038807</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.08439689403097367</v>
+        <v>0.08439368816831395</v>
       </c>
       <c r="C16">
-        <v>701.4779346560325</v>
+        <v>693.9470859417179</v>
       </c>
       <c r="D16">
-        <v>784.3219346560326</v>
+        <v>784.3870859417179</v>
       </c>
       <c r="E16">
-        <v>-152.656</v>
+        <v>-145.06</v>
       </c>
       <c r="F16">
-        <v>106.344</v>
+        <v>113.94</v>
       </c>
       <c r="G16">
         <v>23.5</v>
@@ -2599,45 +2599,45 @@
         <v>71.875</v>
       </c>
       <c r="M16">
-        <v>5.3491032</v>
+        <v>5.902092000000001</v>
       </c>
       <c r="N16">
-        <v>66.5258968</v>
+        <v>65.972908</v>
       </c>
       <c r="O16">
-        <v>15.966215232</v>
+        <v>15.83349792</v>
       </c>
       <c r="P16">
-        <v>50.559681568</v>
+        <v>50.13941008</v>
       </c>
       <c r="Q16">
-        <v>78.059681568</v>
+        <v>77.63941008</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09191276050113217</v>
+        <v>0.09233939784507525</v>
       </c>
       <c r="T16">
-        <v>0.6347595053709079</v>
+        <v>0.6406323289987066</v>
       </c>
       <c r="U16">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V16">
         <v>0.24</v>
       </c>
       <c r="W16">
-        <v>0.038228</v>
+        <v>0.039368</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y16">
-        <v>13.4368318038807</v>
+        <v>12.17788540063421</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.08439368816831395</v>
+        <v>0.08423088230565426</v>
       </c>
       <c r="C17">
-        <v>693.9470859417179</v>
+        <v>689.6740077307677</v>
       </c>
       <c r="D17">
-        <v>784.3870859417179</v>
+        <v>787.7100077307678</v>
       </c>
       <c r="E17">
-        <v>-145.06</v>
+        <v>-137.464</v>
       </c>
       <c r="F17">
-        <v>113.94</v>
+        <v>121.536</v>
       </c>
       <c r="G17">
         <v>23.5</v>
@@ -2681,28 +2681,28 @@
         <v>71.875</v>
       </c>
       <c r="M17">
-        <v>5.902092</v>
+        <v>6.2955648</v>
       </c>
       <c r="N17">
-        <v>65.972908</v>
+        <v>65.57943520000001</v>
       </c>
       <c r="O17">
-        <v>15.83349792</v>
+        <v>15.739064448</v>
       </c>
       <c r="P17">
-        <v>50.13941008</v>
+        <v>49.84037075200001</v>
       </c>
       <c r="Q17">
-        <v>77.63941008</v>
+        <v>77.34037075200001</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09233939784507525</v>
+        <v>0.09277619322101698</v>
       </c>
       <c r="T17">
-        <v>0.6406323289987065</v>
+        <v>0.6466449817605003</v>
       </c>
       <c r="U17">
         <v>0.0518</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>12.17788540063422</v>
+        <v>11.41676756309458</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.08423088230565426</v>
+        <v>0.08406807644299455</v>
       </c>
       <c r="C18">
-        <v>689.6740077307677</v>
+        <v>685.4292032768865</v>
       </c>
       <c r="D18">
-        <v>787.7100077307678</v>
+        <v>791.0612032768864</v>
       </c>
       <c r="E18">
-        <v>-137.464</v>
+        <v>-129.868</v>
       </c>
       <c r="F18">
-        <v>121.536</v>
+        <v>129.132</v>
       </c>
       <c r="G18">
         <v>23.5</v>
@@ -2763,28 +2763,28 @@
         <v>71.875</v>
       </c>
       <c r="M18">
-        <v>6.2955648</v>
+        <v>6.6890376</v>
       </c>
       <c r="N18">
-        <v>65.57943520000001</v>
+        <v>65.18596239999999</v>
       </c>
       <c r="O18">
-        <v>15.739064448</v>
+        <v>15.644630976</v>
       </c>
       <c r="P18">
-        <v>49.84037075200001</v>
+        <v>49.54133142399999</v>
       </c>
       <c r="Q18">
-        <v>77.34037075200001</v>
+        <v>77.04133142399999</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09277619322101698</v>
+        <v>0.09322351378674043</v>
       </c>
       <c r="T18">
-        <v>0.6466449817605003</v>
+        <v>0.6528025177213735</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>11.41676756309458</v>
+        <v>10.7451930005596</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.08406807644299455</v>
+        <v>0.08390527058033484</v>
       </c>
       <c r="C19">
-        <v>685.4292032768865</v>
+        <v>681.2130349813906</v>
       </c>
       <c r="D19">
-        <v>791.0612032768864</v>
+        <v>794.4410349813905</v>
       </c>
       <c r="E19">
-        <v>-129.868</v>
+        <v>-122.272</v>
       </c>
       <c r="F19">
-        <v>129.132</v>
+        <v>136.728</v>
       </c>
       <c r="G19">
         <v>23.5</v>
@@ -2845,28 +2845,28 @@
         <v>71.875</v>
       </c>
       <c r="M19">
-        <v>6.6890376</v>
+        <v>7.0825104</v>
       </c>
       <c r="N19">
-        <v>65.18596239999999</v>
+        <v>64.7924896</v>
       </c>
       <c r="O19">
-        <v>15.644630976</v>
+        <v>15.550197504</v>
       </c>
       <c r="P19">
-        <v>49.54133142399999</v>
+        <v>49.242292096</v>
       </c>
       <c r="Q19">
-        <v>77.04133142399999</v>
+        <v>76.742292096</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09322351378674043</v>
+        <v>0.09368174461016446</v>
       </c>
       <c r="T19">
-        <v>0.6528025177213735</v>
+        <v>0.6591102374861705</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>10.7451930005596</v>
+        <v>10.14823783386185</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.08390527058033485</v>
+        <v>0.08398794471767515</v>
       </c>
       <c r="C20">
-        <v>681.2130349813901</v>
+        <v>671.8971276200386</v>
       </c>
       <c r="D20">
-        <v>794.4410349813902</v>
+        <v>792.7211276200386</v>
       </c>
       <c r="E20">
-        <v>-122.272</v>
+        <v>-114.676</v>
       </c>
       <c r="F20">
-        <v>136.728</v>
+        <v>144.324</v>
       </c>
       <c r="G20">
         <v>23.5</v>
@@ -2927,45 +2927,45 @@
         <v>71.875</v>
       </c>
       <c r="M20">
-        <v>7.0825104</v>
+        <v>7.721334000000001</v>
       </c>
       <c r="N20">
-        <v>64.7924896</v>
+        <v>64.153666</v>
       </c>
       <c r="O20">
-        <v>15.550197504</v>
+        <v>15.39687984</v>
       </c>
       <c r="P20">
-        <v>49.242292096</v>
+        <v>48.75678616</v>
       </c>
       <c r="Q20">
-        <v>76.742292096</v>
+        <v>76.25678616</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09368174461016446</v>
+        <v>0.09415128977490758</v>
       </c>
       <c r="T20">
-        <v>0.6591102374861704</v>
+        <v>0.6655737034179994</v>
       </c>
       <c r="U20">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V20">
         <v>0.24</v>
       </c>
       <c r="W20">
-        <v>0.039368</v>
+        <v>0.04066</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>10.14823783386185</v>
+        <v>9.308624649574801</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.08398794471767515</v>
+        <v>0.08383805885501545</v>
       </c>
       <c r="C21">
-        <v>671.8971276200386</v>
+        <v>667.4247804466663</v>
       </c>
       <c r="D21">
-        <v>792.7211276200386</v>
+        <v>795.8447804466663</v>
       </c>
       <c r="E21">
-        <v>-114.676</v>
+        <v>-107.08</v>
       </c>
       <c r="F21">
-        <v>144.324</v>
+        <v>151.92</v>
       </c>
       <c r="G21">
         <v>23.5</v>
@@ -3009,28 +3009,28 @@
         <v>71.875</v>
       </c>
       <c r="M21">
-        <v>7.721334000000001</v>
+        <v>8.12772</v>
       </c>
       <c r="N21">
-        <v>64.153666</v>
+        <v>63.74728</v>
       </c>
       <c r="O21">
-        <v>15.39687984</v>
+        <v>15.2993472</v>
       </c>
       <c r="P21">
-        <v>48.75678616</v>
+        <v>48.4479328</v>
       </c>
       <c r="Q21">
-        <v>76.25678616</v>
+        <v>75.9479328</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09415128977490758</v>
+        <v>0.09463257356876931</v>
       </c>
       <c r="T21">
-        <v>0.6655737034179994</v>
+        <v>0.6721987559981241</v>
       </c>
       <c r="U21">
         <v>0.0535</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>9.308624649574801</v>
+        <v>8.843193417096062</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.08383805885501545</v>
+        <v>0.08368817299235576</v>
       </c>
       <c r="C22">
-        <v>667.4247804466663</v>
+        <v>662.9771476557298</v>
       </c>
       <c r="D22">
-        <v>795.8447804466663</v>
+        <v>798.9931476557299</v>
       </c>
       <c r="E22">
-        <v>-107.08</v>
+        <v>-99.48399999999998</v>
       </c>
       <c r="F22">
-        <v>151.92</v>
+        <v>159.516</v>
       </c>
       <c r="G22">
         <v>23.5</v>
@@ -3091,28 +3091,28 @@
         <v>71.875</v>
       </c>
       <c r="M22">
-        <v>8.12772</v>
+        <v>8.534106000000001</v>
       </c>
       <c r="N22">
-        <v>63.74728</v>
+        <v>63.340894</v>
       </c>
       <c r="O22">
-        <v>15.2993472</v>
+        <v>15.20181456</v>
       </c>
       <c r="P22">
-        <v>48.4479328</v>
+        <v>48.13907944</v>
       </c>
       <c r="Q22">
-        <v>75.9479328</v>
+        <v>75.63907944</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09463257356876931</v>
+        <v>0.09512604176247563</v>
       </c>
       <c r="T22">
-        <v>0.6721987559981241</v>
+        <v>0.6789915314283785</v>
       </c>
       <c r="U22">
         <v>0.0535</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>8.843193417096062</v>
+        <v>8.422088968662914</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.08368817299235576</v>
+        <v>0.08353828712969605</v>
       </c>
       <c r="C23">
-        <v>662.9771476557299</v>
+        <v>658.5545237229586</v>
       </c>
       <c r="D23">
-        <v>798.9931476557299</v>
+        <v>802.1665237229586</v>
       </c>
       <c r="E23">
-        <v>-99.48400000000001</v>
+        <v>-91.88800000000001</v>
       </c>
       <c r="F23">
-        <v>159.516</v>
+        <v>167.112</v>
       </c>
       <c r="G23">
         <v>23.5</v>
@@ -3173,28 +3173,28 @@
         <v>71.875</v>
       </c>
       <c r="M23">
-        <v>8.534106</v>
+        <v>8.940491999999999</v>
       </c>
       <c r="N23">
-        <v>63.340894</v>
+        <v>62.934508</v>
       </c>
       <c r="O23">
-        <v>15.20181456</v>
+        <v>15.10428192</v>
       </c>
       <c r="P23">
-        <v>48.13907944</v>
+        <v>47.83022608</v>
       </c>
       <c r="Q23">
-        <v>75.63907944</v>
+        <v>75.33022608</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.09512604176247563</v>
+        <v>0.09563216298678981</v>
       </c>
       <c r="T23">
-        <v>0.6789915314283785</v>
+        <v>0.6859584805876139</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>8.422088968662916</v>
+        <v>8.039266742814602</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.08353828712969605</v>
+        <v>0.08338840126703634</v>
       </c>
       <c r="C24">
-        <v>658.5545237229586</v>
+        <v>654.157207821034</v>
       </c>
       <c r="D24">
-        <v>802.1665237229586</v>
+        <v>805.3652078210341</v>
       </c>
       <c r="E24">
-        <v>-91.88800000000001</v>
+        <v>-84.29199999999997</v>
       </c>
       <c r="F24">
-        <v>167.112</v>
+        <v>174.708</v>
       </c>
       <c r="G24">
         <v>23.5</v>
@@ -3255,28 +3255,28 @@
         <v>71.875</v>
       </c>
       <c r="M24">
-        <v>8.940491999999999</v>
+        <v>9.346878000000002</v>
       </c>
       <c r="N24">
-        <v>62.934508</v>
+        <v>62.528122</v>
       </c>
       <c r="O24">
-        <v>15.10428192</v>
+        <v>15.00674928</v>
       </c>
       <c r="P24">
-        <v>47.83022608</v>
+        <v>47.52137272</v>
       </c>
       <c r="Q24">
-        <v>75.33022608</v>
+        <v>75.02137271999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.09563216298678981</v>
+        <v>0.09615143021693032</v>
       </c>
       <c r="T24">
-        <v>0.6859584805876139</v>
+        <v>0.6931063894652708</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.039266742814602</v>
+        <v>7.689733406170486</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.08338840126703634</v>
+        <v>0.08338443540437665</v>
       </c>
       <c r="C25">
-        <v>654.157207821034</v>
+        <v>646.6461889514073</v>
       </c>
       <c r="D25">
-        <v>805.3652078210341</v>
+        <v>805.4501889514074</v>
       </c>
       <c r="E25">
-        <v>-84.29199999999997</v>
+        <v>-76.69599999999997</v>
       </c>
       <c r="F25">
-        <v>174.708</v>
+        <v>182.304</v>
       </c>
       <c r="G25">
         <v>23.5</v>
@@ -3337,45 +3337,45 @@
         <v>71.875</v>
       </c>
       <c r="M25">
-        <v>9.346878000000002</v>
+        <v>9.899107200000001</v>
       </c>
       <c r="N25">
-        <v>62.528122</v>
+        <v>61.9758928</v>
       </c>
       <c r="O25">
-        <v>15.00674928</v>
+        <v>14.874214272</v>
       </c>
       <c r="P25">
-        <v>47.52137272</v>
+        <v>47.101678528</v>
       </c>
       <c r="Q25">
-        <v>75.02137271999999</v>
+        <v>74.60167852800001</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.09615143021693032</v>
+        <v>0.09668436237417979</v>
       </c>
       <c r="T25">
-        <v>0.6931063894652708</v>
+        <v>0.7004424012081293</v>
       </c>
       <c r="U25">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V25">
         <v>0.24</v>
       </c>
       <c r="W25">
-        <v>0.04066</v>
+        <v>0.041268</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y25">
-        <v>7.689733406170486</v>
+        <v>7.26075579826027</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.08338443540437664</v>
+        <v>0.08324062954171693</v>
       </c>
       <c r="C26">
-        <v>646.6461889514078</v>
+        <v>642.1438457800817</v>
       </c>
       <c r="D26">
-        <v>805.4501889514078</v>
+        <v>808.5438457800817</v>
       </c>
       <c r="E26">
-        <v>-76.696</v>
+        <v>-69.09999999999999</v>
       </c>
       <c r="F26">
-        <v>182.304</v>
+        <v>189.9</v>
       </c>
       <c r="G26">
         <v>23.5</v>
@@ -3419,28 +3419,28 @@
         <v>71.875</v>
       </c>
       <c r="M26">
-        <v>9.8991072</v>
+        <v>10.31157</v>
       </c>
       <c r="N26">
-        <v>61.9758928</v>
+        <v>61.56343</v>
       </c>
       <c r="O26">
-        <v>14.874214272</v>
+        <v>14.7752232</v>
       </c>
       <c r="P26">
-        <v>47.101678528</v>
+        <v>46.7882068</v>
       </c>
       <c r="Q26">
-        <v>74.60167852800001</v>
+        <v>74.2882068</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.09668436237417979</v>
+        <v>0.09723150605562259</v>
       </c>
       <c r="T26">
-        <v>0.7004424012081293</v>
+        <v>0.7079740399307974</v>
       </c>
       <c r="U26">
         <v>0.0543</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.260755798260272</v>
+        <v>6.97032556632986</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.08324062954171693</v>
+        <v>0.08309682367905724</v>
       </c>
       <c r="C27">
-        <v>642.1438457800817</v>
+        <v>637.6653591169045</v>
       </c>
       <c r="D27">
-        <v>808.5438457800817</v>
+        <v>811.6613591169045</v>
       </c>
       <c r="E27">
-        <v>-69.09999999999999</v>
+        <v>-61.50399999999999</v>
       </c>
       <c r="F27">
-        <v>189.9</v>
+        <v>197.496</v>
       </c>
       <c r="G27">
         <v>23.5</v>
@@ -3501,28 +3501,28 @@
         <v>71.875</v>
       </c>
       <c r="M27">
-        <v>10.31157</v>
+        <v>10.7240328</v>
       </c>
       <c r="N27">
-        <v>61.56343</v>
+        <v>61.1509672</v>
       </c>
       <c r="O27">
-        <v>14.7752232</v>
+        <v>14.676232128</v>
       </c>
       <c r="P27">
-        <v>46.7882068</v>
+        <v>46.474735072</v>
       </c>
       <c r="Q27">
-        <v>74.2882068</v>
+        <v>73.974735072</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.09723150605562259</v>
+        <v>0.09779343740413139</v>
       </c>
       <c r="T27">
-        <v>0.7079740399307974</v>
+        <v>0.7157092364567808</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>6.97032556632986</v>
+        <v>6.702236121471018</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.08309682367905724</v>
+        <v>0.08295301781639752</v>
       </c>
       <c r="C28">
-        <v>637.6653591169045</v>
+        <v>633.2110059815597</v>
       </c>
       <c r="D28">
-        <v>811.6613591169045</v>
+        <v>814.8030059815596</v>
       </c>
       <c r="E28">
-        <v>-61.50399999999999</v>
+        <v>-53.90799999999999</v>
       </c>
       <c r="F28">
-        <v>197.496</v>
+        <v>205.092</v>
       </c>
       <c r="G28">
         <v>23.5</v>
@@ -3583,28 +3583,28 @@
         <v>71.875</v>
       </c>
       <c r="M28">
-        <v>10.7240328</v>
+        <v>11.1364956</v>
       </c>
       <c r="N28">
-        <v>61.1509672</v>
+        <v>60.7385044</v>
       </c>
       <c r="O28">
-        <v>14.676232128</v>
+        <v>14.577241056</v>
       </c>
       <c r="P28">
-        <v>46.474735072</v>
+        <v>46.161263344</v>
       </c>
       <c r="Q28">
-        <v>73.974735072</v>
+        <v>73.66126334399999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.09779343740413139</v>
+        <v>0.0983707641320514</v>
       </c>
       <c r="T28">
-        <v>0.7157092364567808</v>
+        <v>0.7236563561752568</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>6.702236121471018</v>
+        <v>6.454005154009129</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.08295301781639752</v>
+        <v>0.08280921195373782</v>
       </c>
       <c r="C29">
-        <v>633.2110059815597</v>
+        <v>628.7810676993656</v>
       </c>
       <c r="D29">
-        <v>814.8030059815596</v>
+        <v>817.9690676993656</v>
       </c>
       <c r="E29">
-        <v>-53.90799999999999</v>
+        <v>-46.31199999999998</v>
       </c>
       <c r="F29">
-        <v>205.092</v>
+        <v>212.688</v>
       </c>
       <c r="G29">
         <v>23.5</v>
@@ -3665,28 +3665,28 @@
         <v>71.875</v>
       </c>
       <c r="M29">
-        <v>11.1364956</v>
+        <v>11.5489584</v>
       </c>
       <c r="N29">
-        <v>60.7385044</v>
+        <v>60.3260416</v>
       </c>
       <c r="O29">
-        <v>14.577241056</v>
+        <v>14.478249984</v>
       </c>
       <c r="P29">
-        <v>46.161263344</v>
+        <v>45.84779161599999</v>
       </c>
       <c r="Q29">
-        <v>73.66126334399999</v>
+        <v>73.34779161599999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.0983707641320514</v>
+        <v>0.09896412771352475</v>
       </c>
       <c r="T29">
-        <v>0.7236563561752568</v>
+        <v>0.7318242292192462</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.454005154009129</v>
+        <v>6.223504969937374</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.08280921195373782</v>
+        <v>0.08288580609107812</v>
       </c>
       <c r="C30">
-        <v>628.7810676993656</v>
+        <v>619.4956980532638</v>
       </c>
       <c r="D30">
-        <v>817.9690676993656</v>
+        <v>816.2796980532638</v>
       </c>
       <c r="E30">
-        <v>-46.31199999999998</v>
+        <v>-38.71599999999998</v>
       </c>
       <c r="F30">
-        <v>212.688</v>
+        <v>220.284</v>
       </c>
       <c r="G30">
         <v>23.5</v>
@@ -3747,45 +3747,45 @@
         <v>71.875</v>
       </c>
       <c r="M30">
-        <v>11.5489584</v>
+        <v>12.1817052</v>
       </c>
       <c r="N30">
-        <v>60.3260416</v>
+        <v>59.6932948</v>
       </c>
       <c r="O30">
-        <v>14.478249984</v>
+        <v>14.326390752</v>
       </c>
       <c r="P30">
-        <v>45.84779161599999</v>
+        <v>45.36690404799999</v>
       </c>
       <c r="Q30">
-        <v>73.34779161599999</v>
+        <v>72.86690404799999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.09896412771352475</v>
+        <v>0.09957420576208187</v>
       </c>
       <c r="T30">
-        <v>0.7318242292192462</v>
+        <v>0.7402221831940522</v>
       </c>
       <c r="U30">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V30">
         <v>0.24</v>
       </c>
       <c r="W30">
-        <v>0.041268</v>
+        <v>0.042028</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>6.223504969937374</v>
+        <v>5.900241289700558</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.08288580609107812</v>
+        <v>0.08274960022841842</v>
       </c>
       <c r="C31">
-        <v>619.4956980532638</v>
+        <v>614.908717900776</v>
       </c>
       <c r="D31">
-        <v>816.2796980532638</v>
+        <v>819.288717900776</v>
       </c>
       <c r="E31">
-        <v>-38.71600000000001</v>
+        <v>-31.12</v>
       </c>
       <c r="F31">
-        <v>220.284</v>
+        <v>227.88</v>
       </c>
       <c r="G31">
         <v>23.5</v>
@@ -3829,28 +3829,28 @@
         <v>71.875</v>
       </c>
       <c r="M31">
-        <v>12.1817052</v>
+        <v>12.601764</v>
       </c>
       <c r="N31">
-        <v>59.6932948</v>
+        <v>59.273236</v>
       </c>
       <c r="O31">
-        <v>14.326390752</v>
+        <v>14.22557664</v>
       </c>
       <c r="P31">
-        <v>45.366904048</v>
+        <v>45.04765936</v>
       </c>
       <c r="Q31">
-        <v>72.86690404800001</v>
+        <v>72.54765936</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.09957420576208187</v>
+        <v>0.1002017146120263</v>
       </c>
       <c r="T31">
-        <v>0.7402221831940522</v>
+        <v>0.7488600787109954</v>
       </c>
       <c r="U31">
         <v>0.0553</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>5.900241289700559</v>
+        <v>5.703566580043873</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.08274960022841842</v>
+        <v>0.08261339436575871</v>
       </c>
       <c r="C32">
-        <v>614.908717900776</v>
+        <v>610.3440038908784</v>
       </c>
       <c r="D32">
-        <v>819.288717900776</v>
+        <v>822.3200038908784</v>
       </c>
       <c r="E32">
-        <v>-31.12</v>
+        <v>-23.524</v>
       </c>
       <c r="F32">
-        <v>227.88</v>
+        <v>235.476</v>
       </c>
       <c r="G32">
         <v>23.5</v>
@@ -3911,28 +3911,28 @@
         <v>71.875</v>
       </c>
       <c r="M32">
-        <v>12.601764</v>
+        <v>13.0218228</v>
       </c>
       <c r="N32">
-        <v>59.273236</v>
+        <v>58.8531772</v>
       </c>
       <c r="O32">
-        <v>14.22557664</v>
+        <v>14.124762528</v>
       </c>
       <c r="P32">
-        <v>45.04765936</v>
+        <v>44.728414672</v>
       </c>
       <c r="Q32">
-        <v>72.54765936</v>
+        <v>72.228414672</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1002017146120263</v>
+        <v>0.100847412124288</v>
       </c>
       <c r="T32">
-        <v>0.7488600787109954</v>
+        <v>0.7577483480110384</v>
       </c>
       <c r="U32">
         <v>0.0553</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>5.703566580043873</v>
+        <v>5.51958056133278</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.08261339436575871</v>
+        <v>0.082477188503099</v>
       </c>
       <c r="C33">
-        <v>610.3440038908784</v>
+        <v>605.8018040888634</v>
       </c>
       <c r="D33">
-        <v>822.3200038908784</v>
+        <v>825.3738040888634</v>
       </c>
       <c r="E33">
-        <v>-23.524</v>
+        <v>-15.928</v>
       </c>
       <c r="F33">
-        <v>235.476</v>
+        <v>243.072</v>
       </c>
       <c r="G33">
         <v>23.5</v>
@@ -3993,28 +3993,28 @@
         <v>71.875</v>
       </c>
       <c r="M33">
-        <v>13.0218228</v>
+        <v>13.4418816</v>
       </c>
       <c r="N33">
-        <v>58.8531772</v>
+        <v>58.4331184</v>
       </c>
       <c r="O33">
-        <v>14.124762528</v>
+        <v>14.023948416</v>
       </c>
       <c r="P33">
-        <v>44.728414672</v>
+        <v>44.409169984</v>
       </c>
       <c r="Q33">
-        <v>72.228414672</v>
+        <v>71.909169984</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.100847412124288</v>
+        <v>0.1015121007398515</v>
       </c>
       <c r="T33">
-        <v>0.7577483480110384</v>
+        <v>0.7668980369963768</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.51958056133278</v>
+        <v>5.347093668791131</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.082477188503099</v>
+        <v>0.08234098264043931</v>
       </c>
       <c r="C34">
-        <v>605.8018040888634</v>
+        <v>601.2823702586583</v>
       </c>
       <c r="D34">
-        <v>825.3738040888634</v>
+        <v>828.4503702586583</v>
       </c>
       <c r="E34">
-        <v>-15.928</v>
+        <v>-8.331999999999994</v>
       </c>
       <c r="F34">
-        <v>243.072</v>
+        <v>250.668</v>
       </c>
       <c r="G34">
         <v>23.5</v>
@@ -4075,28 +4075,28 @@
         <v>71.875</v>
       </c>
       <c r="M34">
-        <v>13.4418816</v>
+        <v>13.8619404</v>
       </c>
       <c r="N34">
-        <v>58.4331184</v>
+        <v>58.0130596</v>
       </c>
       <c r="O34">
-        <v>14.023948416</v>
+        <v>13.923134304</v>
       </c>
       <c r="P34">
-        <v>44.409169984</v>
+        <v>44.089925296</v>
       </c>
       <c r="Q34">
-        <v>71.909169984</v>
+        <v>71.58992529599999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1015121007398515</v>
+        <v>0.1021966308066258</v>
       </c>
       <c r="T34">
-        <v>0.7668980369963768</v>
+        <v>0.7763208510260537</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.347093668791131</v>
+        <v>5.185060527312611</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.08234098264043931</v>
+        <v>0.0822047767777796</v>
       </c>
       <c r="C35">
-        <v>601.2823702586583</v>
+        <v>596.7859579320184</v>
       </c>
       <c r="D35">
-        <v>828.4503702586583</v>
+        <v>831.5499579320184</v>
       </c>
       <c r="E35">
-        <v>-8.331999999999994</v>
+        <v>-0.73599999999999</v>
       </c>
       <c r="F35">
-        <v>250.668</v>
+        <v>258.264</v>
       </c>
       <c r="G35">
         <v>23.5</v>
@@ -4157,28 +4157,28 @@
         <v>71.875</v>
       </c>
       <c r="M35">
-        <v>13.8619404</v>
+        <v>14.2819992</v>
       </c>
       <c r="N35">
-        <v>58.0130596</v>
+        <v>57.5930008</v>
       </c>
       <c r="O35">
-        <v>13.923134304</v>
+        <v>13.822320192</v>
       </c>
       <c r="P35">
-        <v>44.089925296</v>
+        <v>43.770680608</v>
       </c>
       <c r="Q35">
-        <v>71.58992529599999</v>
+        <v>71.27068060799999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1021966308066258</v>
+        <v>0.102901904208757</v>
       </c>
       <c r="T35">
-        <v>0.7763208510260537</v>
+        <v>0.7860292048748118</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.185060527312611</v>
+        <v>5.032558747097535</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.0822047767777796</v>
+        <v>0.0820685709151199</v>
       </c>
       <c r="C36">
-        <v>596.7859579320184</v>
+        <v>592.3128264792746</v>
       </c>
       <c r="D36">
-        <v>831.5499579320184</v>
+        <v>834.6728264792746</v>
       </c>
       <c r="E36">
-        <v>-0.73599999999999</v>
+        <v>6.860000000000014</v>
       </c>
       <c r="F36">
-        <v>258.264</v>
+        <v>265.86</v>
       </c>
       <c r="G36">
         <v>23.5</v>
@@ -4239,28 +4239,28 @@
         <v>71.875</v>
       </c>
       <c r="M36">
-        <v>14.2819992</v>
+        <v>14.702058</v>
       </c>
       <c r="N36">
-        <v>57.5930008</v>
+        <v>57.172942</v>
       </c>
       <c r="O36">
-        <v>13.822320192</v>
+        <v>13.72150608</v>
       </c>
       <c r="P36">
-        <v>43.770680608</v>
+        <v>43.45143592</v>
       </c>
       <c r="Q36">
-        <v>71.27068060799999</v>
+        <v>70.95143591999999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.102901904208757</v>
+        <v>0.1036288783309537</v>
       </c>
       <c r="T36">
-        <v>0.7860292048748118</v>
+        <v>0.7960362773035315</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.032558747097535</v>
+        <v>4.888771354323319</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.0820685709151199</v>
+        <v>0.0819323650524602</v>
       </c>
       <c r="C37">
-        <v>592.3128264792746</v>
+        <v>587.8632391816859</v>
       </c>
       <c r="D37">
-        <v>834.6728264792746</v>
+        <v>837.8192391816859</v>
       </c>
       <c r="E37">
-        <v>6.860000000000014</v>
+        <v>14.45600000000002</v>
       </c>
       <c r="F37">
-        <v>265.86</v>
+        <v>273.456</v>
       </c>
       <c r="G37">
         <v>23.5</v>
@@ -4321,28 +4321,28 @@
         <v>71.875</v>
       </c>
       <c r="M37">
-        <v>14.702058</v>
+        <v>15.1221168</v>
       </c>
       <c r="N37">
-        <v>57.172942</v>
+        <v>56.7528832</v>
       </c>
       <c r="O37">
-        <v>13.72150608</v>
+        <v>13.620691968</v>
       </c>
       <c r="P37">
-        <v>43.45143592</v>
+        <v>43.132191232</v>
       </c>
       <c r="Q37">
-        <v>70.95143591999999</v>
+        <v>70.632191232</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1036288783309537</v>
+        <v>0.1043785703944691</v>
       </c>
       <c r="T37">
-        <v>0.7960362773035315</v>
+        <v>0.806356070745649</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>4.888771354323319</v>
+        <v>4.752972150036561</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.08193236505246021</v>
+        <v>0.0817961591898005</v>
       </c>
       <c r="C38">
-        <v>587.8632391816857</v>
+        <v>583.43746330543</v>
       </c>
       <c r="D38">
-        <v>837.8192391816857</v>
+        <v>840.98946330543</v>
       </c>
       <c r="E38">
-        <v>14.45600000000002</v>
+        <v>22.05200000000002</v>
       </c>
       <c r="F38">
-        <v>273.456</v>
+        <v>281.052</v>
       </c>
       <c r="G38">
         <v>23.5</v>
@@ -4403,28 +4403,28 @@
         <v>71.875</v>
       </c>
       <c r="M38">
-        <v>15.1221168</v>
+        <v>15.5421756</v>
       </c>
       <c r="N38">
-        <v>56.7528832</v>
+        <v>56.3328244</v>
       </c>
       <c r="O38">
-        <v>13.620691968</v>
+        <v>13.519877856</v>
       </c>
       <c r="P38">
-        <v>43.132191232</v>
+        <v>42.812946544</v>
       </c>
       <c r="Q38">
-        <v>70.632191232</v>
+        <v>70.312946544</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1043785703944691</v>
+        <v>0.1051520622060325</v>
       </c>
       <c r="T38">
-        <v>0.8063560707456489</v>
+        <v>0.817003476677992</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>4.752972150036561</v>
+        <v>4.624513443278816</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.0817961591898005</v>
+        <v>0.08165995332714079</v>
       </c>
       <c r="C39">
-        <v>583.43746330543</v>
+        <v>579.0357701772837</v>
       </c>
       <c r="D39">
-        <v>840.98946330543</v>
+        <v>844.1837701772837</v>
       </c>
       <c r="E39">
-        <v>22.05200000000002</v>
+        <v>29.64800000000002</v>
       </c>
       <c r="F39">
-        <v>281.052</v>
+        <v>288.648</v>
       </c>
       <c r="G39">
         <v>23.5</v>
@@ -4485,28 +4485,28 @@
         <v>71.875</v>
       </c>
       <c r="M39">
-        <v>15.5421756</v>
+        <v>15.9622344</v>
       </c>
       <c r="N39">
-        <v>56.3328244</v>
+        <v>55.9127656</v>
       </c>
       <c r="O39">
-        <v>13.519877856</v>
+        <v>13.419063744</v>
       </c>
       <c r="P39">
-        <v>42.812946544</v>
+        <v>42.493701856</v>
       </c>
       <c r="Q39">
-        <v>70.312946544</v>
+        <v>69.993701856</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1051520622060325</v>
+        <v>0.1059505053663561</v>
       </c>
       <c r="T39">
-        <v>0.817003476677992</v>
+        <v>0.8279943473178303</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.624513443278816</v>
+        <v>4.502815721087268</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.08165995332714079</v>
+        <v>0.08226474746448109</v>
       </c>
       <c r="C40">
-        <v>579.0357701772837</v>
+        <v>557.4383734710988</v>
       </c>
       <c r="D40">
-        <v>844.1837701772837</v>
+        <v>830.1823734710988</v>
       </c>
       <c r="E40">
-        <v>29.64800000000002</v>
+        <v>37.24400000000003</v>
       </c>
       <c r="F40">
-        <v>288.648</v>
+        <v>296.244</v>
       </c>
       <c r="G40">
         <v>23.5</v>
@@ -4567,45 +4567,45 @@
         <v>71.875</v>
       </c>
       <c r="M40">
-        <v>15.9622344</v>
+        <v>17.1229032</v>
       </c>
       <c r="N40">
-        <v>55.9127656</v>
+        <v>54.7520968</v>
       </c>
       <c r="O40">
-        <v>13.419063744</v>
+        <v>13.140503232</v>
       </c>
       <c r="P40">
-        <v>42.493701856</v>
+        <v>41.611593568</v>
       </c>
       <c r="Q40">
-        <v>69.993701856</v>
+        <v>69.11159356799999</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1059505053663561</v>
+        <v>0.1067751269909526</v>
       </c>
       <c r="T40">
-        <v>0.8279943473178303</v>
+        <v>0.8393455743720893</v>
       </c>
       <c r="U40">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V40">
         <v>0.24</v>
       </c>
       <c r="W40">
-        <v>0.042028</v>
+        <v>0.043928</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y40">
-        <v>4.502815721087268</v>
+        <v>4.197594249087386</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.08226474746448109</v>
+        <v>0.08214754160182139</v>
       </c>
       <c r="C41">
-        <v>557.4383734710988</v>
+        <v>552.5193699599805</v>
       </c>
       <c r="D41">
-        <v>830.1823734710988</v>
+        <v>832.8593699599805</v>
       </c>
       <c r="E41">
-        <v>37.24400000000003</v>
+        <v>44.84000000000003</v>
       </c>
       <c r="F41">
-        <v>296.244</v>
+        <v>303.84</v>
       </c>
       <c r="G41">
         <v>23.5</v>
@@ -4649,28 +4649,28 @@
         <v>71.875</v>
       </c>
       <c r="M41">
-        <v>17.1229032</v>
+        <v>17.561952</v>
       </c>
       <c r="N41">
-        <v>54.7520968</v>
+        <v>54.31304799999999</v>
       </c>
       <c r="O41">
-        <v>13.140503232</v>
+        <v>13.03513152</v>
       </c>
       <c r="P41">
-        <v>41.611593568</v>
+        <v>41.27791647999999</v>
       </c>
       <c r="Q41">
-        <v>69.11159356799999</v>
+        <v>68.77791647999999</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1067751269909526</v>
+        <v>0.1076272360030357</v>
       </c>
       <c r="T41">
-        <v>0.8393455743720893</v>
+        <v>0.8510751756614905</v>
       </c>
       <c r="U41">
         <v>0.0578</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.197594249087386</v>
+        <v>4.092654392860201</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.08214754160182139</v>
+        <v>0.08312093573916168</v>
       </c>
       <c r="C42">
-        <v>552.5193699599805</v>
+        <v>523.2009663843035</v>
       </c>
       <c r="D42">
-        <v>832.8593699599805</v>
+        <v>811.1369663843035</v>
       </c>
       <c r="E42">
-        <v>44.84000000000003</v>
+        <v>52.43600000000004</v>
       </c>
       <c r="F42">
-        <v>303.84</v>
+        <v>311.436</v>
       </c>
       <c r="G42">
         <v>23.5</v>
@@ -4731,45 +4731,45 @@
         <v>71.875</v>
       </c>
       <c r="M42">
-        <v>17.561952</v>
+        <v>19.0910268</v>
       </c>
       <c r="N42">
-        <v>54.31304799999999</v>
+        <v>52.7839732</v>
       </c>
       <c r="O42">
-        <v>13.03513152</v>
+        <v>12.668153568</v>
       </c>
       <c r="P42">
-        <v>41.27791647999999</v>
+        <v>40.115819632</v>
       </c>
       <c r="Q42">
-        <v>68.77791647999999</v>
+        <v>67.615819632</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1076272360030357</v>
+        <v>0.1085082300663757</v>
       </c>
       <c r="T42">
-        <v>0.8510751756614905</v>
+        <v>0.863202390553922</v>
       </c>
       <c r="U42">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V42">
         <v>0.24</v>
       </c>
       <c r="W42">
-        <v>0.043928</v>
+        <v>0.046588</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y42">
-        <v>4.092654392860201</v>
+        <v>3.764857739343805</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.08312093573916168</v>
+        <v>0.08303032987650197</v>
       </c>
       <c r="C43">
-        <v>523.2009663843035</v>
+        <v>517.5789957527841</v>
       </c>
       <c r="D43">
-        <v>811.1369663843035</v>
+        <v>813.1109957527841</v>
       </c>
       <c r="E43">
-        <v>52.43600000000004</v>
+        <v>60.03200000000004</v>
       </c>
       <c r="F43">
-        <v>311.436</v>
+        <v>319.032</v>
       </c>
       <c r="G43">
         <v>23.5</v>
@@ -4813,28 +4813,28 @@
         <v>71.875</v>
       </c>
       <c r="M43">
-        <v>19.0910268</v>
+        <v>19.5566616</v>
       </c>
       <c r="N43">
-        <v>52.7839732</v>
+        <v>52.3183384</v>
       </c>
       <c r="O43">
-        <v>12.668153568</v>
+        <v>12.556401216</v>
       </c>
       <c r="P43">
-        <v>40.115819632</v>
+        <v>39.761937184</v>
       </c>
       <c r="Q43">
-        <v>67.615819632</v>
+        <v>67.261937184</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1085082300663757</v>
+        <v>0.1094196032353482</v>
       </c>
       <c r="T43">
-        <v>0.863202390553922</v>
+        <v>0.8757477852702307</v>
       </c>
       <c r="U43">
         <v>0.0613</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.764857739343805</v>
+        <v>3.675218269359429</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08303032987650198</v>
+        <v>0.08293972401384229</v>
       </c>
       <c r="C44">
-        <v>517.5789957527838</v>
+        <v>511.9666567832427</v>
       </c>
       <c r="D44">
-        <v>813.1109957527838</v>
+        <v>815.0946567832427</v>
       </c>
       <c r="E44">
-        <v>60.03199999999998</v>
+        <v>67.62799999999999</v>
       </c>
       <c r="F44">
-        <v>319.032</v>
+        <v>326.628</v>
       </c>
       <c r="G44">
         <v>23.5</v>
@@ -4895,28 +4895,28 @@
         <v>71.875</v>
       </c>
       <c r="M44">
-        <v>19.5566616</v>
+        <v>20.0222964</v>
       </c>
       <c r="N44">
-        <v>52.3183384</v>
+        <v>51.8527036</v>
       </c>
       <c r="O44">
-        <v>12.556401216</v>
+        <v>12.444648864</v>
       </c>
       <c r="P44">
-        <v>39.761937184</v>
+        <v>39.408054736</v>
       </c>
       <c r="Q44">
-        <v>67.261937184</v>
+        <v>66.908054736</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1094196032353482</v>
+        <v>0.1103629544102496</v>
       </c>
       <c r="T44">
-        <v>0.8757477852702306</v>
+        <v>0.8887333692748307</v>
       </c>
       <c r="U44">
         <v>0.0613</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.675218269359429</v>
+        <v>3.589748077048744</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08293972401384229</v>
+        <v>0.08284911815118257</v>
       </c>
       <c r="C45">
-        <v>511.9666567832427</v>
+        <v>506.3640201401199</v>
       </c>
       <c r="D45">
-        <v>815.0946567832427</v>
+        <v>817.0880201401199</v>
       </c>
       <c r="E45">
-        <v>67.62799999999999</v>
+        <v>75.22399999999999</v>
       </c>
       <c r="F45">
-        <v>326.628</v>
+        <v>334.224</v>
       </c>
       <c r="G45">
         <v>23.5</v>
@@ -4977,28 +4977,28 @@
         <v>71.875</v>
       </c>
       <c r="M45">
-        <v>20.0222964</v>
+        <v>20.4879312</v>
       </c>
       <c r="N45">
-        <v>51.8527036</v>
+        <v>51.3870688</v>
       </c>
       <c r="O45">
-        <v>12.444648864</v>
+        <v>12.332896512</v>
       </c>
       <c r="P45">
-        <v>39.408054736</v>
+        <v>39.054172288</v>
       </c>
       <c r="Q45">
-        <v>66.908054736</v>
+        <v>66.554172288</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1103629544102496</v>
+        <v>0.1113399966985403</v>
       </c>
       <c r="T45">
-        <v>0.8887333692748307</v>
+        <v>0.9021827241367378</v>
       </c>
       <c r="U45">
         <v>0.0613</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.589748077048744</v>
+        <v>3.508162893479455</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08284911815118257</v>
+        <v>0.08371611228852288</v>
       </c>
       <c r="C46">
-        <v>506.3640201401199</v>
+        <v>480.0843925107407</v>
       </c>
       <c r="D46">
-        <v>817.0880201401199</v>
+        <v>798.4043925107406</v>
       </c>
       <c r="E46">
-        <v>75.22399999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="F46">
-        <v>334.224</v>
+        <v>341.82</v>
       </c>
       <c r="G46">
         <v>23.5</v>
@@ -5059,45 +5059,45 @@
         <v>71.875</v>
       </c>
       <c r="M46">
-        <v>20.4879312</v>
+        <v>21.910662</v>
       </c>
       <c r="N46">
-        <v>51.3870688</v>
+        <v>49.964338</v>
       </c>
       <c r="O46">
-        <v>12.332896512</v>
+        <v>11.99144112</v>
       </c>
       <c r="P46">
-        <v>39.054172288</v>
+        <v>37.97289688</v>
       </c>
       <c r="Q46">
-        <v>66.554172288</v>
+        <v>65.47289688000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1113399966985403</v>
+        <v>0.1123525677973143</v>
       </c>
       <c r="T46">
-        <v>0.9021827241367378</v>
+        <v>0.9161211464481691</v>
       </c>
       <c r="U46">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V46">
         <v>0.24</v>
       </c>
       <c r="W46">
-        <v>0.046588</v>
+        <v>0.048716</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.508162893479455</v>
+        <v>3.280366426171879</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.08371611228852288</v>
+        <v>0.08364678642586319</v>
       </c>
       <c r="C47">
-        <v>480.0843925107407</v>
+        <v>473.950870001941</v>
       </c>
       <c r="D47">
-        <v>798.4043925107406</v>
+        <v>799.866870001941</v>
       </c>
       <c r="E47">
-        <v>82.81999999999999</v>
+        <v>90.41600000000005</v>
       </c>
       <c r="F47">
-        <v>341.82</v>
+        <v>349.4160000000001</v>
       </c>
       <c r="G47">
         <v>23.5</v>
@@ -5141,28 +5141,28 @@
         <v>71.875</v>
       </c>
       <c r="M47">
-        <v>21.910662</v>
+        <v>22.3975656</v>
       </c>
       <c r="N47">
-        <v>49.964338</v>
+        <v>49.47743439999999</v>
       </c>
       <c r="O47">
-        <v>11.99144112</v>
+        <v>11.874584256</v>
       </c>
       <c r="P47">
-        <v>37.97289688</v>
+        <v>37.60285014399999</v>
       </c>
       <c r="Q47">
-        <v>65.47289688000001</v>
+        <v>65.102850144</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1123525677973143</v>
+        <v>0.1134026415293763</v>
       </c>
       <c r="T47">
-        <v>0.9161211464481691</v>
+        <v>0.9305758066229867</v>
       </c>
       <c r="U47">
         <v>0.0641</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.280366426171879</v>
+        <v>3.209054112559446</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.08364678642586319</v>
+        <v>0.08357746056320348</v>
       </c>
       <c r="C48">
-        <v>473.950870001941</v>
+        <v>467.8227151124677</v>
       </c>
       <c r="D48">
-        <v>799.866870001941</v>
+        <v>801.3347151124677</v>
       </c>
       <c r="E48">
-        <v>90.41600000000005</v>
+        <v>98.01200000000006</v>
       </c>
       <c r="F48">
-        <v>349.4160000000001</v>
+        <v>357.0120000000001</v>
       </c>
       <c r="G48">
         <v>23.5</v>
@@ -5223,28 +5223,28 @@
         <v>71.875</v>
       </c>
       <c r="M48">
-        <v>22.3975656</v>
+        <v>22.88446920000001</v>
       </c>
       <c r="N48">
-        <v>49.47743439999999</v>
+        <v>48.99053079999999</v>
       </c>
       <c r="O48">
-        <v>11.874584256</v>
+        <v>11.757727392</v>
       </c>
       <c r="P48">
-        <v>37.60285014399999</v>
+        <v>37.232803408</v>
       </c>
       <c r="Q48">
-        <v>65.102850144</v>
+        <v>64.732803408</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1134026415293763</v>
+        <v>0.1144923406852896</v>
       </c>
       <c r="T48">
-        <v>0.9305758066229867</v>
+        <v>0.9455759256723254</v>
       </c>
       <c r="U48">
         <v>0.0641</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.209054112559446</v>
+        <v>3.140776365483713</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.08357746056320348</v>
+        <v>0.08350813470054377</v>
       </c>
       <c r="C49">
-        <v>467.8227151124677</v>
+        <v>461.6999574471922</v>
       </c>
       <c r="D49">
-        <v>801.3347151124677</v>
+        <v>802.8079574471923</v>
       </c>
       <c r="E49">
-        <v>98.01200000000006</v>
+        <v>105.6080000000001</v>
       </c>
       <c r="F49">
-        <v>357.0120000000001</v>
+        <v>364.6080000000001</v>
       </c>
       <c r="G49">
         <v>23.5</v>
@@ -5305,28 +5305,28 @@
         <v>71.875</v>
       </c>
       <c r="M49">
-        <v>22.88446920000001</v>
+        <v>23.37137280000001</v>
       </c>
       <c r="N49">
-        <v>48.99053079999999</v>
+        <v>48.5036272</v>
       </c>
       <c r="O49">
-        <v>11.757727392</v>
+        <v>11.640870528</v>
       </c>
       <c r="P49">
-        <v>37.232803408</v>
+        <v>36.862756672</v>
       </c>
       <c r="Q49">
-        <v>64.732803408</v>
+        <v>64.36275667199999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1144923406852896</v>
+        <v>0.1156239513471995</v>
       </c>
       <c r="T49">
-        <v>0.9455759256723254</v>
+        <v>0.9611529723774082</v>
       </c>
       <c r="U49">
         <v>0.0641</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>3.140776365483713</v>
+        <v>3.075343524536136</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.08350813470054377</v>
+        <v>0.08343880883788407</v>
       </c>
       <c r="C50">
-        <v>461.6999574471923</v>
+        <v>455.5826268291011</v>
       </c>
       <c r="D50">
-        <v>802.8079574471923</v>
+        <v>804.2866268291011</v>
       </c>
       <c r="E50">
-        <v>105.608</v>
+        <v>113.204</v>
       </c>
       <c r="F50">
-        <v>364.608</v>
+        <v>372.204</v>
       </c>
       <c r="G50">
         <v>23.5</v>
@@ -5387,28 +5387,28 @@
         <v>71.875</v>
       </c>
       <c r="M50">
-        <v>23.3713728</v>
+        <v>23.8582764</v>
       </c>
       <c r="N50">
-        <v>48.5036272</v>
+        <v>48.0167236</v>
       </c>
       <c r="O50">
-        <v>11.640870528</v>
+        <v>11.524013664</v>
       </c>
       <c r="P50">
-        <v>36.862756672</v>
+        <v>36.492709936</v>
       </c>
       <c r="Q50">
-        <v>64.36275667199999</v>
+        <v>63.992709936</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1156239513471995</v>
+        <v>0.1167999388978119</v>
       </c>
       <c r="T50">
-        <v>0.9611529723774082</v>
+        <v>0.9773408836591607</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.075343524536136</v>
+        <v>3.012581411790501</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08343880883788407</v>
+        <v>0.08633348297522436</v>
       </c>
       <c r="C51">
-        <v>455.5826268291011</v>
+        <v>390.548984494888</v>
       </c>
       <c r="D51">
-        <v>804.2866268291011</v>
+        <v>746.848984494888</v>
       </c>
       <c r="E51">
-        <v>113.204</v>
+        <v>120.8</v>
       </c>
       <c r="F51">
-        <v>372.204</v>
+        <v>379.8</v>
       </c>
       <c r="G51">
         <v>23.5</v>
@@ -5469,45 +5469,45 @@
         <v>71.875</v>
       </c>
       <c r="M51">
-        <v>23.8582764</v>
+        <v>27.30762</v>
       </c>
       <c r="N51">
-        <v>48.0167236</v>
+        <v>44.56738</v>
       </c>
       <c r="O51">
-        <v>11.524013664</v>
+        <v>10.6961712</v>
       </c>
       <c r="P51">
-        <v>36.492709936</v>
+        <v>33.8712088</v>
       </c>
       <c r="Q51">
-        <v>63.992709936</v>
+        <v>61.3712088</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1167999388978119</v>
+        <v>0.1180229659504487</v>
       </c>
       <c r="T51">
-        <v>0.9773408836591607</v>
+        <v>0.9941763113921835</v>
       </c>
       <c r="U51">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V51">
         <v>0.24</v>
       </c>
       <c r="W51">
-        <v>0.048716</v>
+        <v>0.05464400000000001</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>3.012581411790501</v>
+        <v>2.6320492228909</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08633348297522436</v>
+        <v>0.08632343711256467</v>
       </c>
       <c r="C52">
-        <v>390.548984494888</v>
+        <v>383.138130249058</v>
       </c>
       <c r="D52">
-        <v>746.848984494888</v>
+        <v>747.034130249058</v>
       </c>
       <c r="E52">
-        <v>120.8</v>
+        <v>128.396</v>
       </c>
       <c r="F52">
-        <v>379.8</v>
+        <v>387.396</v>
       </c>
       <c r="G52">
         <v>23.5</v>
@@ -5551,28 +5551,28 @@
         <v>71.875</v>
       </c>
       <c r="M52">
-        <v>27.30762</v>
+        <v>27.8537724</v>
       </c>
       <c r="N52">
-        <v>44.56738</v>
+        <v>44.0212276</v>
       </c>
       <c r="O52">
-        <v>10.6961712</v>
+        <v>10.565094624</v>
       </c>
       <c r="P52">
-        <v>33.8712088</v>
+        <v>33.456132976</v>
       </c>
       <c r="Q52">
-        <v>61.3712088</v>
+        <v>60.956132976</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1180229659504487</v>
+        <v>0.1192959124746218</v>
       </c>
       <c r="T52">
-        <v>0.9941763113921835</v>
+        <v>1.01169889944084</v>
       </c>
       <c r="U52">
         <v>0.07190000000000001</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.6320492228909</v>
+        <v>2.580440414598921</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08632343711256467</v>
+        <v>0.08631339124990496</v>
       </c>
       <c r="C53">
-        <v>383.138130249058</v>
+        <v>375.7273678221928</v>
       </c>
       <c r="D53">
-        <v>747.034130249058</v>
+        <v>747.2193678221928</v>
       </c>
       <c r="E53">
-        <v>128.396</v>
+        <v>135.992</v>
       </c>
       <c r="F53">
-        <v>387.396</v>
+        <v>394.992</v>
       </c>
       <c r="G53">
         <v>23.5</v>
@@ -5633,28 +5633,28 @@
         <v>71.875</v>
       </c>
       <c r="M53">
-        <v>27.8537724</v>
+        <v>28.3999248</v>
       </c>
       <c r="N53">
-        <v>44.0212276</v>
+        <v>43.47507519999999</v>
       </c>
       <c r="O53">
-        <v>10.565094624</v>
+        <v>10.434018048</v>
       </c>
       <c r="P53">
-        <v>33.456132976</v>
+        <v>33.04105715199999</v>
       </c>
       <c r="Q53">
-        <v>60.956132976</v>
+        <v>60.54105715199999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1192959124746218</v>
+        <v>0.120621898437302</v>
       </c>
       <c r="T53">
-        <v>1.01169889944084</v>
+        <v>1.029951595324857</v>
       </c>
       <c r="U53">
         <v>0.07190000000000001</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>2.580440414598921</v>
+        <v>2.530816560472019</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.08631339124990496</v>
+        <v>0.08787426538724526</v>
       </c>
       <c r="C54">
-        <v>375.7273678221928</v>
+        <v>340.4109697256643</v>
       </c>
       <c r="D54">
-        <v>747.2193678221928</v>
+        <v>719.4989697256643</v>
       </c>
       <c r="E54">
-        <v>135.992</v>
+        <v>143.588</v>
       </c>
       <c r="F54">
-        <v>394.992</v>
+        <v>402.588</v>
       </c>
       <c r="G54">
         <v>23.5</v>
@@ -5715,45 +5715,45 @@
         <v>71.875</v>
       </c>
       <c r="M54">
-        <v>28.3999248</v>
+        <v>30.5161704</v>
       </c>
       <c r="N54">
-        <v>43.47507519999999</v>
+        <v>41.35882959999999</v>
       </c>
       <c r="O54">
-        <v>10.434018048</v>
+        <v>9.926119103999998</v>
       </c>
       <c r="P54">
-        <v>33.04105715199999</v>
+        <v>31.432710496</v>
       </c>
       <c r="Q54">
-        <v>60.54105715199999</v>
+        <v>58.932710496</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.120621898437302</v>
+        <v>0.1220043093345644</v>
       </c>
       <c r="T54">
-        <v>1.029951595324857</v>
+        <v>1.048981001672024</v>
       </c>
       <c r="U54">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V54">
         <v>0.24</v>
       </c>
       <c r="W54">
-        <v>0.05464400000000001</v>
+        <v>0.05760800000000001</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y54">
-        <v>2.530816560472019</v>
+        <v>2.35530864646109</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.08787426538724526</v>
+        <v>0.08789385952458556</v>
       </c>
       <c r="C55">
-        <v>340.4109697256643</v>
+        <v>332.480052429217</v>
       </c>
       <c r="D55">
-        <v>719.4989697256643</v>
+        <v>719.164052429217</v>
       </c>
       <c r="E55">
-        <v>143.588</v>
+        <v>151.184</v>
       </c>
       <c r="F55">
-        <v>402.588</v>
+        <v>410.184</v>
       </c>
       <c r="G55">
         <v>23.5</v>
@@ -5797,28 +5797,28 @@
         <v>71.875</v>
       </c>
       <c r="M55">
-        <v>30.5161704</v>
+        <v>31.0919472</v>
       </c>
       <c r="N55">
-        <v>41.35882959999999</v>
+        <v>40.78305279999999</v>
       </c>
       <c r="O55">
-        <v>9.926119103999998</v>
+        <v>9.787932671999998</v>
       </c>
       <c r="P55">
-        <v>31.432710496</v>
+        <v>30.995120128</v>
       </c>
       <c r="Q55">
-        <v>58.932710496</v>
+        <v>58.495120128</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1220043093345644</v>
+        <v>0.1234468250534469</v>
       </c>
       <c r="T55">
-        <v>1.048981001672024</v>
+        <v>1.068837773512545</v>
       </c>
       <c r="U55">
         <v>0.07580000000000001</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>2.35530864646109</v>
+        <v>2.311691819674774</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.08789385952458556</v>
+        <v>0.08791345366192585</v>
       </c>
       <c r="C56">
-        <v>332.480052429217</v>
+        <v>324.5494467868818</v>
       </c>
       <c r="D56">
-        <v>719.164052429217</v>
+        <v>718.8294467868818</v>
       </c>
       <c r="E56">
-        <v>151.184</v>
+        <v>158.78</v>
       </c>
       <c r="F56">
-        <v>410.184</v>
+        <v>417.78</v>
       </c>
       <c r="G56">
         <v>23.5</v>
@@ -5879,28 +5879,28 @@
         <v>71.875</v>
       </c>
       <c r="M56">
-        <v>31.0919472</v>
+        <v>31.667724</v>
       </c>
       <c r="N56">
-        <v>40.78305279999999</v>
+        <v>40.20727599999999</v>
       </c>
       <c r="O56">
-        <v>9.787932671999998</v>
+        <v>9.649746239999997</v>
       </c>
       <c r="P56">
-        <v>30.995120128</v>
+        <v>30.55752975999999</v>
       </c>
       <c r="Q56">
-        <v>58.495120128</v>
+        <v>58.05752975999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1234468250534469</v>
+        <v>0.1249534525820575</v>
       </c>
       <c r="T56">
-        <v>1.068837773512545</v>
+        <v>1.089577068545979</v>
       </c>
       <c r="U56">
         <v>0.07580000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.311691819674774</v>
+        <v>2.269661059317051</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.08791345366192585</v>
+        <v>0.08793304779926615</v>
       </c>
       <c r="C57">
-        <v>324.5494467868818</v>
+        <v>316.6191523638508</v>
       </c>
       <c r="D57">
-        <v>718.8294467868818</v>
+        <v>718.4951523638508</v>
       </c>
       <c r="E57">
-        <v>158.78</v>
+        <v>166.376</v>
       </c>
       <c r="F57">
-        <v>417.78</v>
+        <v>425.376</v>
       </c>
       <c r="G57">
         <v>23.5</v>
@@ -5961,28 +5961,28 @@
         <v>71.875</v>
       </c>
       <c r="M57">
-        <v>31.667724</v>
+        <v>32.24350080000001</v>
       </c>
       <c r="N57">
-        <v>40.20727599999999</v>
+        <v>39.63149919999999</v>
       </c>
       <c r="O57">
-        <v>9.649746239999997</v>
+        <v>9.511559807999998</v>
       </c>
       <c r="P57">
-        <v>30.55752975999999</v>
+        <v>30.119939392</v>
       </c>
       <c r="Q57">
-        <v>58.05752975999999</v>
+        <v>57.61993939199999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1249534525820575</v>
+        <v>0.1265285631801503</v>
       </c>
       <c r="T57">
-        <v>1.089577068545979</v>
+        <v>1.111259058808205</v>
       </c>
       <c r="U57">
         <v>0.07580000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.269661059317051</v>
+        <v>2.229131397543532</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.08793304779926615</v>
+        <v>0.08795264193660646</v>
       </c>
       <c r="C58">
-        <v>316.6191523638508</v>
+        <v>308.6891687261245</v>
       </c>
       <c r="D58">
-        <v>718.4951523638508</v>
+        <v>718.1611687261245</v>
       </c>
       <c r="E58">
-        <v>166.376</v>
+        <v>173.972</v>
       </c>
       <c r="F58">
-        <v>425.376</v>
+        <v>432.972</v>
       </c>
       <c r="G58">
         <v>23.5</v>
@@ -6043,28 +6043,28 @@
         <v>71.875</v>
       </c>
       <c r="M58">
-        <v>32.24350080000001</v>
+        <v>32.81927760000001</v>
       </c>
       <c r="N58">
-        <v>39.63149919999999</v>
+        <v>39.05572239999999</v>
       </c>
       <c r="O58">
-        <v>9.511559807999998</v>
+        <v>9.373373375999998</v>
       </c>
       <c r="P58">
-        <v>30.119939392</v>
+        <v>29.682349024</v>
       </c>
       <c r="Q58">
-        <v>57.61993939199999</v>
+        <v>57.182349024</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1265285631801503</v>
+        <v>0.1281769347362941</v>
       </c>
       <c r="T58">
-        <v>1.111259058808205</v>
+        <v>1.133949513733791</v>
       </c>
       <c r="U58">
         <v>0.07580000000000001</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.229131397543532</v>
+        <v>2.190023829165575</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.08795264193660646</v>
+        <v>0.08797223607394675</v>
       </c>
       <c r="C59">
-        <v>308.6891687261245</v>
+        <v>300.7594954405105</v>
       </c>
       <c r="D59">
-        <v>718.1611687261245</v>
+        <v>717.8274954405106</v>
       </c>
       <c r="E59">
-        <v>173.972</v>
+        <v>181.568</v>
       </c>
       <c r="F59">
-        <v>432.972</v>
+        <v>440.568</v>
       </c>
       <c r="G59">
         <v>23.5</v>
@@ -6125,28 +6125,28 @@
         <v>71.875</v>
       </c>
       <c r="M59">
-        <v>32.81927760000001</v>
+        <v>33.39505440000001</v>
       </c>
       <c r="N59">
-        <v>39.05572239999999</v>
+        <v>38.47994559999999</v>
       </c>
       <c r="O59">
-        <v>9.373373375999998</v>
+        <v>9.235186943999999</v>
       </c>
       <c r="P59">
-        <v>29.682349024</v>
+        <v>29.24475865599999</v>
       </c>
       <c r="Q59">
-        <v>57.182349024</v>
+        <v>56.74475865599999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1281769347362941</v>
+        <v>0.1299038001760637</v>
       </c>
       <c r="T59">
-        <v>1.133949513733791</v>
+        <v>1.157720466512976</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.190023829165575</v>
+        <v>2.152264797628238</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.08797223607394675</v>
+        <v>0.08799183021128705</v>
       </c>
       <c r="C60">
-        <v>300.7594954405106</v>
+        <v>292.8301320746203</v>
       </c>
       <c r="D60">
-        <v>717.8274954405106</v>
+        <v>717.4941320746203</v>
       </c>
       <c r="E60">
-        <v>181.568</v>
+        <v>189.164</v>
       </c>
       <c r="F60">
-        <v>440.568</v>
+        <v>448.164</v>
       </c>
       <c r="G60">
         <v>23.5</v>
@@ -6207,28 +6207,28 @@
         <v>71.875</v>
       </c>
       <c r="M60">
-        <v>33.3950544</v>
+        <v>33.9708312</v>
       </c>
       <c r="N60">
-        <v>38.4799456</v>
+        <v>37.9041688</v>
       </c>
       <c r="O60">
-        <v>9.235186944000001</v>
+        <v>9.097000511999999</v>
       </c>
       <c r="P60">
-        <v>29.244758656</v>
+        <v>28.807168288</v>
       </c>
       <c r="Q60">
-        <v>56.744758656</v>
+        <v>56.307168288</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1299038001760637</v>
+        <v>0.1317149029543586</v>
       </c>
       <c r="T60">
-        <v>1.157720466512976</v>
+        <v>1.182650977964316</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.152264797628238</v>
+        <v>2.115785733261658</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.08799183021128705</v>
+        <v>0.08801142434862733</v>
       </c>
       <c r="C61">
-        <v>292.8301320746203</v>
+        <v>284.901078196869</v>
       </c>
       <c r="D61">
-        <v>717.4941320746203</v>
+        <v>717.161078196869</v>
       </c>
       <c r="E61">
-        <v>189.164</v>
+        <v>196.76</v>
       </c>
       <c r="F61">
-        <v>448.164</v>
+        <v>455.76</v>
       </c>
       <c r="G61">
         <v>23.5</v>
@@ -6289,28 +6289,28 @@
         <v>71.875</v>
       </c>
       <c r="M61">
-        <v>33.9708312</v>
+        <v>34.546608</v>
       </c>
       <c r="N61">
-        <v>37.9041688</v>
+        <v>37.328392</v>
       </c>
       <c r="O61">
-        <v>9.097000511999999</v>
+        <v>8.95881408</v>
       </c>
       <c r="P61">
-        <v>28.807168288</v>
+        <v>28.36957792</v>
       </c>
       <c r="Q61">
-        <v>56.307168288</v>
+        <v>55.86957792</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1317149029543586</v>
+        <v>0.1336165608715683</v>
       </c>
       <c r="T61">
-        <v>1.182650977964316</v>
+        <v>1.208828014988223</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.115785733261658</v>
+        <v>2.080522637707297</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.08801142434862733</v>
+        <v>0.08803101848596764</v>
       </c>
       <c r="C62">
-        <v>284.901078196869</v>
+        <v>276.9723333764714</v>
       </c>
       <c r="D62">
-        <v>717.161078196869</v>
+        <v>716.8283333764714</v>
       </c>
       <c r="E62">
-        <v>196.76</v>
+        <v>204.356</v>
       </c>
       <c r="F62">
-        <v>455.76</v>
+        <v>463.356</v>
       </c>
       <c r="G62">
         <v>23.5</v>
@@ -6371,28 +6371,28 @@
         <v>71.875</v>
       </c>
       <c r="M62">
-        <v>34.546608</v>
+        <v>35.1223848</v>
       </c>
       <c r="N62">
-        <v>37.328392</v>
+        <v>36.7526152</v>
       </c>
       <c r="O62">
-        <v>8.95881408</v>
+        <v>8.820627648</v>
       </c>
       <c r="P62">
-        <v>28.36957792</v>
+        <v>27.931987552</v>
       </c>
       <c r="Q62">
-        <v>55.86957792</v>
+        <v>55.431987552</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1336165608715683</v>
+        <v>0.1356157397076093</v>
       </c>
       <c r="T62">
-        <v>1.208828014988223</v>
+        <v>1.236347464167203</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.080522637707297</v>
+        <v>2.046415709220292</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.08803101848596764</v>
+        <v>0.08805061262330795</v>
       </c>
       <c r="C63">
-        <v>276.9723333764714</v>
+        <v>269.0438971834433</v>
       </c>
       <c r="D63">
-        <v>716.8283333764714</v>
+        <v>716.4958971834433</v>
       </c>
       <c r="E63">
-        <v>204.356</v>
+        <v>211.952</v>
       </c>
       <c r="F63">
-        <v>463.356</v>
+        <v>470.952</v>
       </c>
       <c r="G63">
         <v>23.5</v>
@@ -6453,28 +6453,28 @@
         <v>71.875</v>
       </c>
       <c r="M63">
-        <v>35.1223848</v>
+        <v>35.69816160000001</v>
       </c>
       <c r="N63">
-        <v>36.7526152</v>
+        <v>36.17683839999999</v>
       </c>
       <c r="O63">
-        <v>8.820627648</v>
+        <v>8.682441215999999</v>
       </c>
       <c r="P63">
-        <v>27.931987552</v>
+        <v>27.49439718399999</v>
       </c>
       <c r="Q63">
-        <v>55.431987552</v>
+        <v>54.99439718399999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1356157397076093</v>
+        <v>0.1377201384823893</v>
       </c>
       <c r="T63">
-        <v>1.236347464167203</v>
+        <v>1.265315305408234</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.046415709220292</v>
+        <v>2.013409004232868</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.08805061262330795</v>
+        <v>0.09486916676064822</v>
       </c>
       <c r="C64">
-        <v>269.0438971834433</v>
+        <v>161.8850477069474</v>
       </c>
       <c r="D64">
-        <v>716.4958971834433</v>
+        <v>616.9330477069474</v>
       </c>
       <c r="E64">
-        <v>211.952</v>
+        <v>219.548</v>
       </c>
       <c r="F64">
-        <v>470.952</v>
+        <v>478.548</v>
       </c>
       <c r="G64">
         <v>23.5</v>
@@ -6535,45 +6535,45 @@
         <v>71.875</v>
       </c>
       <c r="M64">
-        <v>35.69816160000001</v>
+        <v>43.06932</v>
       </c>
       <c r="N64">
-        <v>36.17683839999999</v>
+        <v>28.80568</v>
       </c>
       <c r="O64">
-        <v>8.682441215999999</v>
+        <v>6.9133632</v>
       </c>
       <c r="P64">
-        <v>27.49439718399999</v>
+        <v>21.8923168</v>
       </c>
       <c r="Q64">
-        <v>54.99439718399999</v>
+        <v>49.3923168</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1377201384823893</v>
+        <v>0.1399382885422925</v>
       </c>
       <c r="T64">
-        <v>1.265315305408234</v>
+        <v>1.295848975905536</v>
       </c>
       <c r="U64">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V64">
         <v>0.24</v>
       </c>
       <c r="W64">
-        <v>0.05760800000000001</v>
+        <v>0.0684</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y64">
-        <v>2.013409004232868</v>
+        <v>1.668821332679504</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09486916676064822</v>
+        <v>0.09499668089798852</v>
       </c>
       <c r="C65">
-        <v>161.8850477069474</v>
+        <v>152.6900031385101</v>
       </c>
       <c r="D65">
-        <v>616.9330477069474</v>
+        <v>615.3340031385101</v>
       </c>
       <c r="E65">
-        <v>219.548</v>
+        <v>227.144</v>
       </c>
       <c r="F65">
-        <v>478.548</v>
+        <v>486.144</v>
       </c>
       <c r="G65">
         <v>23.5</v>
@@ -6617,28 +6617,28 @@
         <v>71.875</v>
       </c>
       <c r="M65">
-        <v>43.06932</v>
+        <v>43.75296</v>
       </c>
       <c r="N65">
-        <v>28.80568</v>
+        <v>28.12204</v>
       </c>
       <c r="O65">
-        <v>6.9133632</v>
+        <v>6.749289599999999</v>
       </c>
       <c r="P65">
-        <v>21.8923168</v>
+        <v>21.3727504</v>
       </c>
       <c r="Q65">
-        <v>49.3923168</v>
+        <v>48.8727504</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1399382885422925</v>
+        <v>0.1422796691610792</v>
       </c>
       <c r="T65">
-        <v>1.295848975905536</v>
+        <v>1.328078961430467</v>
       </c>
       <c r="U65">
         <v>0.09</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.668821332679504</v>
+        <v>1.642745999356386</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09499668089798852</v>
+        <v>0.09512419503532883</v>
       </c>
       <c r="C66">
-        <v>152.6900031385101</v>
+        <v>143.5032263497521</v>
       </c>
       <c r="D66">
-        <v>615.3340031385101</v>
+        <v>613.7432263497521</v>
       </c>
       <c r="E66">
-        <v>227.144</v>
+        <v>234.74</v>
       </c>
       <c r="F66">
-        <v>486.144</v>
+        <v>493.74</v>
       </c>
       <c r="G66">
         <v>23.5</v>
@@ -6699,28 +6699,28 @@
         <v>71.875</v>
       </c>
       <c r="M66">
-        <v>43.75296</v>
+        <v>44.4366</v>
       </c>
       <c r="N66">
-        <v>28.12204</v>
+        <v>27.4384</v>
       </c>
       <c r="O66">
-        <v>6.749289599999999</v>
+        <v>6.585216</v>
       </c>
       <c r="P66">
-        <v>21.3727504</v>
+        <v>20.853184</v>
       </c>
       <c r="Q66">
-        <v>48.8727504</v>
+        <v>48.353184</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1422796691610792</v>
+        <v>0.1447548429580824</v>
       </c>
       <c r="T66">
-        <v>1.328078961430467</v>
+        <v>1.362150660413966</v>
       </c>
       <c r="U66">
         <v>0.09</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>1.642745999356386</v>
+        <v>1.617472983981673</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.09512419503532883</v>
+        <v>0.09525170917266912</v>
       </c>
       <c r="C67">
-        <v>143.5032263497521</v>
+        <v>134.3246533838072</v>
       </c>
       <c r="D67">
-        <v>613.7432263497521</v>
+        <v>612.1606533838072</v>
       </c>
       <c r="E67">
-        <v>234.74</v>
+        <v>242.336</v>
       </c>
       <c r="F67">
-        <v>493.74</v>
+        <v>501.336</v>
       </c>
       <c r="G67">
         <v>23.5</v>
@@ -6781,28 +6781,28 @@
         <v>71.875</v>
       </c>
       <c r="M67">
-        <v>44.4366</v>
+        <v>45.12024</v>
       </c>
       <c r="N67">
-        <v>27.4384</v>
+        <v>26.75476</v>
       </c>
       <c r="O67">
-        <v>6.585216</v>
+        <v>6.421142399999999</v>
       </c>
       <c r="P67">
-        <v>20.853184</v>
+        <v>20.3336176</v>
       </c>
       <c r="Q67">
-        <v>48.353184</v>
+        <v>47.8336176</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1447548429580824</v>
+        <v>0.1473756152137327</v>
       </c>
       <c r="T67">
-        <v>1.362150660413966</v>
+        <v>1.398226576984729</v>
       </c>
       <c r="U67">
         <v>0.09</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>1.617472983981673</v>
+        <v>1.592965817557708</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.09525170917266912</v>
+        <v>0.09537922331000942</v>
       </c>
       <c r="C68">
-        <v>134.3246533838072</v>
+        <v>125.1542209417776</v>
       </c>
       <c r="D68">
-        <v>612.1606533838072</v>
+        <v>610.5862209417777</v>
       </c>
       <c r="E68">
-        <v>242.336</v>
+        <v>249.9320000000001</v>
       </c>
       <c r="F68">
-        <v>501.336</v>
+        <v>508.9320000000001</v>
       </c>
       <c r="G68">
         <v>23.5</v>
@@ -6863,28 +6863,28 @@
         <v>71.875</v>
       </c>
       <c r="M68">
-        <v>45.12024</v>
+        <v>45.80388000000001</v>
       </c>
       <c r="N68">
-        <v>26.75476</v>
+        <v>26.07111999999999</v>
       </c>
       <c r="O68">
-        <v>6.421142399999999</v>
+        <v>6.257068799999998</v>
       </c>
       <c r="P68">
-        <v>20.3336176</v>
+        <v>19.81405119999999</v>
       </c>
       <c r="Q68">
-        <v>47.8336176</v>
+        <v>47.31405119999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1473756152137327</v>
+        <v>0.1501552221515437</v>
       </c>
       <c r="T68">
-        <v>1.398226576984729</v>
+        <v>1.436488912741599</v>
       </c>
       <c r="U68">
         <v>0.09</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>1.592965817557708</v>
+        <v>1.569190208340429</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.09537922331000942</v>
+        <v>0.09550673744734971</v>
       </c>
       <c r="C69">
-        <v>125.1542209417776</v>
+        <v>115.9918663742963</v>
       </c>
       <c r="D69">
-        <v>610.5862209417777</v>
+        <v>609.0198663742963</v>
       </c>
       <c r="E69">
-        <v>249.9320000000001</v>
+        <v>257.528</v>
       </c>
       <c r="F69">
-        <v>508.9320000000001</v>
+        <v>516.528</v>
       </c>
       <c r="G69">
         <v>23.5</v>
@@ -6945,28 +6945,28 @@
         <v>71.875</v>
       </c>
       <c r="M69">
-        <v>45.80388000000001</v>
+        <v>46.48752</v>
       </c>
       <c r="N69">
-        <v>26.07111999999999</v>
+        <v>25.38748</v>
       </c>
       <c r="O69">
-        <v>6.257068799999998</v>
+        <v>6.092995199999999</v>
       </c>
       <c r="P69">
-        <v>19.81405119999999</v>
+        <v>19.2944848</v>
       </c>
       <c r="Q69">
-        <v>47.31405119999999</v>
+        <v>46.7944848</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1501552221515437</v>
+        <v>0.1531085545229678</v>
       </c>
       <c r="T69">
-        <v>1.436488912741599</v>
+        <v>1.477142644483273</v>
       </c>
       <c r="U69">
         <v>0.09</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>1.569190208340429</v>
+        <v>1.546113881747187</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.09550673744734971</v>
+        <v>0.09563425158469002</v>
       </c>
       <c r="C70">
-        <v>115.9918663742963</v>
+        <v>106.837527673215</v>
       </c>
       <c r="D70">
-        <v>609.0198663742963</v>
+        <v>607.4615276732151</v>
       </c>
       <c r="E70">
-        <v>257.528</v>
+        <v>265.124</v>
       </c>
       <c r="F70">
-        <v>516.528</v>
+        <v>524.124</v>
       </c>
       <c r="G70">
         <v>23.5</v>
@@ -7027,28 +7027,28 @@
         <v>71.875</v>
       </c>
       <c r="M70">
-        <v>46.48752</v>
+        <v>47.17116</v>
       </c>
       <c r="N70">
-        <v>25.38748</v>
+        <v>24.70384</v>
       </c>
       <c r="O70">
-        <v>6.092995199999999</v>
+        <v>5.9289216</v>
       </c>
       <c r="P70">
-        <v>19.2944848</v>
+        <v>18.7749184</v>
       </c>
       <c r="Q70">
-        <v>46.7944848</v>
+        <v>46.2749184</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1531085545229678</v>
+        <v>0.156252424466742</v>
       </c>
       <c r="T70">
-        <v>1.477142644483273</v>
+        <v>1.520419197627636</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.546113881747187</v>
+        <v>1.523706434185634</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.09563425158469002</v>
+        <v>0.09576176572203031</v>
       </c>
       <c r="C71">
-        <v>106.837527673215</v>
+        <v>97.69114346342508</v>
       </c>
       <c r="D71">
-        <v>607.4615276732151</v>
+        <v>605.9111434634251</v>
       </c>
       <c r="E71">
-        <v>265.124</v>
+        <v>272.72</v>
       </c>
       <c r="F71">
-        <v>524.124</v>
+        <v>531.72</v>
       </c>
       <c r="G71">
         <v>23.5</v>
@@ -7109,28 +7109,28 @@
         <v>71.875</v>
       </c>
       <c r="M71">
-        <v>47.17116</v>
+        <v>47.8548</v>
       </c>
       <c r="N71">
-        <v>24.70384</v>
+        <v>24.0202</v>
       </c>
       <c r="O71">
-        <v>5.9289216</v>
+        <v>5.764848000000001</v>
       </c>
       <c r="P71">
-        <v>18.7749184</v>
+        <v>18.255352</v>
       </c>
       <c r="Q71">
-        <v>46.2749184</v>
+        <v>45.755352</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.156252424466742</v>
+        <v>0.159605885740101</v>
       </c>
       <c r="T71">
-        <v>1.520419197627636</v>
+        <v>1.566580854314956</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.523706434185634</v>
+        <v>1.501939199411553</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.09576176572203031</v>
+        <v>0.1294883995574272</v>
       </c>
       <c r="C72">
-        <v>97.69114346342508</v>
+        <v>-154.0885591817045</v>
       </c>
       <c r="D72">
-        <v>605.9111434634251</v>
+        <v>361.7274408182956</v>
       </c>
       <c r="E72">
-        <v>272.72</v>
+        <v>280.316</v>
       </c>
       <c r="F72">
-        <v>531.72</v>
+        <v>539.316</v>
       </c>
       <c r="G72">
         <v>23.5</v>
@@ -7191,45 +7191,45 @@
         <v>71.875</v>
       </c>
       <c r="M72">
-        <v>47.8548</v>
+        <v>79.17158880000001</v>
       </c>
       <c r="N72">
-        <v>24.0202</v>
+        <v>-7.296588800000009</v>
       </c>
       <c r="O72">
-        <v>5.764848000000001</v>
+        <v>-1.751181312000002</v>
       </c>
       <c r="P72">
-        <v>18.255352</v>
+        <v>-5.545407488000007</v>
       </c>
       <c r="Q72">
-        <v>45.755352</v>
+        <v>21.95459251199999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.159605885740101</v>
+        <v>0.1654128284569998</v>
       </c>
       <c r="T72">
-        <v>1.566580854314956</v>
+        <v>1.646515606575241</v>
       </c>
       <c r="U72">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V72">
-        <v>0.24</v>
+        <v>0.2178811902281794</v>
       </c>
       <c r="W72">
-        <v>0.0684</v>
+        <v>0.1148150412745033</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y72">
-        <v>1.501939199411553</v>
+        <v>0.9078382926174142</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1294883995574272</v>
+        <v>0.1304983995574272</v>
       </c>
       <c r="C73">
-        <v>-154.0885591817045</v>
+        <v>-165.9980375606998</v>
       </c>
       <c r="D73">
-        <v>361.7274408182956</v>
+        <v>357.4139624393002</v>
       </c>
       <c r="E73">
-        <v>280.316</v>
+        <v>287.912</v>
       </c>
       <c r="F73">
-        <v>539.316</v>
+        <v>546.912</v>
       </c>
       <c r="G73">
         <v>23.5</v>
@@ -7273,37 +7273,37 @@
         <v>71.875</v>
       </c>
       <c r="M73">
-        <v>79.17158880000001</v>
+        <v>80.28668160000001</v>
       </c>
       <c r="N73">
-        <v>-7.296588800000009</v>
+        <v>-8.411681600000009</v>
       </c>
       <c r="O73">
-        <v>-1.751181312000002</v>
+        <v>-2.018803584000002</v>
       </c>
       <c r="P73">
-        <v>-5.545407488000007</v>
+        <v>-6.392878016000006</v>
       </c>
       <c r="Q73">
-        <v>21.95459251199999</v>
+        <v>21.107121984</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1654128284569997</v>
+        <v>0.1696847151876069</v>
       </c>
       <c r="T73">
-        <v>1.64651560657524</v>
+        <v>1.705319735381499</v>
       </c>
       <c r="U73">
         <v>0.1468</v>
       </c>
       <c r="V73">
-        <v>0.2178811902281794</v>
+        <v>0.2148550625861214</v>
       </c>
       <c r="W73">
-        <v>0.1148150412745033</v>
+        <v>0.1152592768123574</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.9078382926174142</v>
+        <v>0.8952294274421724</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1304983995574272</v>
+        <v>0.1315083995574272</v>
       </c>
       <c r="C74">
-        <v>-165.9980375606998</v>
+        <v>-177.8058546512969</v>
       </c>
       <c r="D74">
-        <v>357.4139624393002</v>
+        <v>353.2021453487031</v>
       </c>
       <c r="E74">
-        <v>287.912</v>
+        <v>295.508</v>
       </c>
       <c r="F74">
-        <v>546.912</v>
+        <v>554.508</v>
       </c>
       <c r="G74">
         <v>23.5</v>
@@ -7355,37 +7355,37 @@
         <v>71.875</v>
       </c>
       <c r="M74">
-        <v>80.28668160000001</v>
+        <v>81.40177440000001</v>
       </c>
       <c r="N74">
-        <v>-8.411681600000009</v>
+        <v>-9.526774400000008</v>
       </c>
       <c r="O74">
-        <v>-2.018803584000002</v>
+        <v>-2.286425856000002</v>
       </c>
       <c r="P74">
-        <v>-6.392878016000006</v>
+        <v>-7.240348544000006</v>
       </c>
       <c r="Q74">
-        <v>21.107121984</v>
+        <v>20.25965145599999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1696847151876069</v>
+        <v>0.174273037972333</v>
       </c>
       <c r="T74">
-        <v>1.705319735381499</v>
+        <v>1.768479725580813</v>
       </c>
       <c r="U74">
         <v>0.1468</v>
       </c>
       <c r="V74">
-        <v>0.2148550625861214</v>
+        <v>0.211911842550695</v>
       </c>
       <c r="W74">
-        <v>0.1152592768123574</v>
+        <v>0.115691341513558</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8952294274421724</v>
+        <v>0.882966010627896</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1315083995574272</v>
+        <v>0.1325183995574273</v>
       </c>
       <c r="C75">
-        <v>-177.8058546512969</v>
+        <v>-189.515562568219</v>
       </c>
       <c r="D75">
-        <v>353.2021453487031</v>
+        <v>349.0884374317811</v>
       </c>
       <c r="E75">
-        <v>295.508</v>
+        <v>303.104</v>
       </c>
       <c r="F75">
-        <v>554.508</v>
+        <v>562.104</v>
       </c>
       <c r="G75">
         <v>23.5</v>
@@ -7437,37 +7437,37 @@
         <v>71.875</v>
       </c>
       <c r="M75">
-        <v>81.40177440000001</v>
+        <v>82.51686720000001</v>
       </c>
       <c r="N75">
-        <v>-9.526774400000008</v>
+        <v>-10.64186720000001</v>
       </c>
       <c r="O75">
-        <v>-2.286425856000002</v>
+        <v>-2.554048128000002</v>
       </c>
       <c r="P75">
-        <v>-7.240348544000006</v>
+        <v>-8.087819072000006</v>
       </c>
       <c r="Q75">
-        <v>20.25965145599999</v>
+        <v>19.41218092799999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.174273037972333</v>
+        <v>0.1792143086635767</v>
       </c>
       <c r="T75">
-        <v>1.768479725580813</v>
+        <v>1.836498176564691</v>
       </c>
       <c r="U75">
         <v>0.1468</v>
       </c>
       <c r="V75">
-        <v>0.211911842550695</v>
+        <v>0.2090481690027127</v>
       </c>
       <c r="W75">
-        <v>0.115691341513558</v>
+        <v>0.1161117287904018</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.882966010627896</v>
+        <v>0.8710340375113028</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1325183995574273</v>
+        <v>0.1335283995574273</v>
       </c>
       <c r="C76">
-        <v>-189.515562568219</v>
+        <v>-201.1305498469656</v>
       </c>
       <c r="D76">
-        <v>349.0884374317811</v>
+        <v>345.0694501530345</v>
       </c>
       <c r="E76">
-        <v>303.104</v>
+        <v>310.7</v>
       </c>
       <c r="F76">
-        <v>562.104</v>
+        <v>569.7</v>
       </c>
       <c r="G76">
         <v>23.5</v>
@@ -7519,37 +7519,37 @@
         <v>71.875</v>
       </c>
       <c r="M76">
-        <v>82.51686720000001</v>
+        <v>83.63196000000002</v>
       </c>
       <c r="N76">
-        <v>-10.64186720000001</v>
+        <v>-11.75696000000002</v>
       </c>
       <c r="O76">
-        <v>-2.554048128000002</v>
+        <v>-2.821670400000005</v>
       </c>
       <c r="P76">
-        <v>-8.087819072000006</v>
+        <v>-8.935289600000015</v>
       </c>
       <c r="Q76">
-        <v>19.41218092799999</v>
+        <v>18.56471039999998</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1792143086635767</v>
+        <v>0.1845508810101197</v>
       </c>
       <c r="T76">
-        <v>1.836498176564691</v>
+        <v>1.909958103627279</v>
       </c>
       <c r="U76">
         <v>0.1468</v>
       </c>
       <c r="V76">
-        <v>0.2090481690027127</v>
+        <v>0.2062608600826765</v>
       </c>
       <c r="W76">
-        <v>0.1161117287904018</v>
+        <v>0.1165209057398631</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8710340375113028</v>
+        <v>0.8594202503444853</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1335283995574273</v>
+        <v>0.1345383995574273</v>
       </c>
       <c r="C77">
-        <v>-201.1305498469656</v>
+        <v>-212.654050752918</v>
       </c>
       <c r="D77">
-        <v>345.0694501530345</v>
+        <v>341.141949247082</v>
       </c>
       <c r="E77">
-        <v>310.7</v>
+        <v>318.296</v>
       </c>
       <c r="F77">
-        <v>569.7</v>
+        <v>577.296</v>
       </c>
       <c r="G77">
         <v>23.5</v>
@@ -7601,37 +7601,37 @@
         <v>71.875</v>
       </c>
       <c r="M77">
-        <v>83.63196000000002</v>
+        <v>84.74705280000002</v>
       </c>
       <c r="N77">
-        <v>-11.75696000000002</v>
+        <v>-12.87205280000002</v>
       </c>
       <c r="O77">
-        <v>-2.821670400000005</v>
+        <v>-3.089292672000005</v>
       </c>
       <c r="P77">
-        <v>-8.935289600000015</v>
+        <v>-9.782760128000016</v>
       </c>
       <c r="Q77">
-        <v>18.56471039999998</v>
+        <v>17.71723987199999</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1845508810101197</v>
+        <v>0.1903321677188747</v>
       </c>
       <c r="T77">
-        <v>1.909958103627279</v>
+        <v>1.989539691278415</v>
       </c>
       <c r="U77">
         <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2062608600826765</v>
+        <v>0.2035469013973781</v>
       </c>
       <c r="W77">
-        <v>0.1165209057398631</v>
+        <v>0.1169193148748649</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8594202503444853</v>
+        <v>0.8481120891557421</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1345383995574273</v>
+        <v>0.1355483995574273</v>
       </c>
       <c r="C78">
-        <v>-212.654050752918</v>
+        <v>-224.0891539618736</v>
       </c>
       <c r="D78">
-        <v>341.141949247082</v>
+        <v>337.3028460381264</v>
       </c>
       <c r="E78">
-        <v>318.296</v>
+        <v>325.8920000000001</v>
       </c>
       <c r="F78">
-        <v>577.296</v>
+        <v>584.8920000000001</v>
       </c>
       <c r="G78">
         <v>23.5</v>
@@ -7683,37 +7683,37 @@
         <v>71.875</v>
       </c>
       <c r="M78">
-        <v>84.74705280000002</v>
+        <v>85.86214560000002</v>
       </c>
       <c r="N78">
-        <v>-12.87205280000002</v>
+        <v>-13.98714560000002</v>
       </c>
       <c r="O78">
-        <v>-3.089292672000005</v>
+        <v>-3.356914944000005</v>
       </c>
       <c r="P78">
-        <v>-9.782760128000016</v>
+        <v>-10.63023065600001</v>
       </c>
       <c r="Q78">
-        <v>17.71723987199999</v>
+        <v>16.86976934399998</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.1903321677188747</v>
+        <v>0.1966161750109997</v>
       </c>
       <c r="T78">
-        <v>1.989539691278415</v>
+        <v>2.076041416986173</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.2035469013973781</v>
+        <v>0.2009034351454641</v>
       </c>
       <c r="W78">
-        <v>0.1169193148748649</v>
+        <v>0.1173073757206459</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8481120891557421</v>
+        <v>0.8370976464394337</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1355483995574273</v>
+        <v>0.1365583995574273</v>
       </c>
       <c r="C79">
-        <v>-224.0891539618736</v>
+        <v>-235.4388106609756</v>
       </c>
       <c r="D79">
-        <v>337.3028460381264</v>
+        <v>333.5491893390245</v>
       </c>
       <c r="E79">
-        <v>325.8920000000001</v>
+        <v>333.4880000000001</v>
       </c>
       <c r="F79">
-        <v>584.8920000000001</v>
+        <v>592.4880000000001</v>
       </c>
       <c r="G79">
         <v>23.5</v>
@@ -7765,37 +7765,37 @@
         <v>71.875</v>
       </c>
       <c r="M79">
-        <v>85.86214560000002</v>
+        <v>86.97723840000002</v>
       </c>
       <c r="N79">
-        <v>-13.98714560000002</v>
+        <v>-15.10223840000002</v>
       </c>
       <c r="O79">
-        <v>-3.356914944000005</v>
+        <v>-3.624537216000004</v>
       </c>
       <c r="P79">
-        <v>-10.63023065600001</v>
+        <v>-11.47770118400001</v>
       </c>
       <c r="Q79">
-        <v>16.86976934399998</v>
+        <v>16.02229881599999</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1966161750109997</v>
+        <v>0.2034714556933178</v>
       </c>
       <c r="T79">
-        <v>2.076041416986173</v>
+        <v>2.170406935940089</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.2009034351454641</v>
+        <v>0.1983277500794966</v>
       </c>
       <c r="W79">
-        <v>0.1173073757206459</v>
+        <v>0.1176854862883299</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.8370976464394337</v>
+        <v>0.8263656253312359</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1365583995574273</v>
+        <v>0.1375683995574273</v>
       </c>
       <c r="C80">
-        <v>-235.4388106609756</v>
+        <v>-246.7058421146908</v>
       </c>
       <c r="D80">
-        <v>333.5491893390245</v>
+        <v>329.8781578853093</v>
       </c>
       <c r="E80">
-        <v>333.4880000000001</v>
+        <v>341.0840000000001</v>
       </c>
       <c r="F80">
-        <v>592.4880000000001</v>
+        <v>600.0840000000001</v>
       </c>
       <c r="G80">
         <v>23.5</v>
@@ -7847,37 +7847,37 @@
         <v>71.875</v>
       </c>
       <c r="M80">
-        <v>86.97723840000002</v>
+        <v>88.09233120000002</v>
       </c>
       <c r="N80">
-        <v>-15.10223840000002</v>
+        <v>-16.21733120000002</v>
       </c>
       <c r="O80">
-        <v>-3.624537216000004</v>
+        <v>-3.892159488000004</v>
       </c>
       <c r="P80">
-        <v>-11.47770118400001</v>
+        <v>-12.32517171200001</v>
       </c>
       <c r="Q80">
-        <v>16.02229881599999</v>
+        <v>15.17482828799999</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2034714556933178</v>
+        <v>0.2109796202501425</v>
       </c>
       <c r="T80">
-        <v>2.170406935940089</v>
+        <v>2.273759647175332</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.1983277500794966</v>
+        <v>0.1958172722303891</v>
       </c>
       <c r="W80">
-        <v>0.1176854862883299</v>
+        <v>0.1180540244365789</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8263656253312359</v>
+        <v>0.8159053009599544</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1375683995574273</v>
+        <v>0.1385783995574272</v>
       </c>
       <c r="C81">
-        <v>-246.7058421146908</v>
+        <v>-257.8929467366015</v>
       </c>
       <c r="D81">
-        <v>329.8781578853093</v>
+        <v>326.2870532633986</v>
       </c>
       <c r="E81">
-        <v>341.0840000000001</v>
+        <v>348.6800000000001</v>
       </c>
       <c r="F81">
-        <v>600.0840000000001</v>
+        <v>607.6800000000001</v>
       </c>
       <c r="G81">
         <v>23.5</v>
@@ -7929,37 +7929,37 @@
         <v>71.875</v>
       </c>
       <c r="M81">
-        <v>88.09233120000002</v>
+        <v>89.20742400000002</v>
       </c>
       <c r="N81">
-        <v>-16.21733120000002</v>
+        <v>-17.33242400000002</v>
       </c>
       <c r="O81">
-        <v>-3.892159488000004</v>
+        <v>-4.159781760000004</v>
       </c>
       <c r="P81">
-        <v>-12.32517171200001</v>
+        <v>-13.17264224000001</v>
       </c>
       <c r="Q81">
-        <v>15.17482828799999</v>
+        <v>14.32735775999999</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2109796202501425</v>
+        <v>0.2192386012626497</v>
       </c>
       <c r="T81">
-        <v>2.273759647175332</v>
+        <v>2.387447629534099</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1958172722303891</v>
+        <v>0.1933695563275092</v>
       </c>
       <c r="W81">
-        <v>0.1180540244365789</v>
+        <v>0.1184133491311217</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8159053009599544</v>
+        <v>0.805706484697955</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1385783995574272</v>
+        <v>0.1850355460524805</v>
       </c>
       <c r="C82">
-        <v>-257.8929467366015</v>
+        <v>-374.3574495195294</v>
       </c>
       <c r="D82">
-        <v>326.2870532633986</v>
+        <v>217.4185504804707</v>
       </c>
       <c r="E82">
-        <v>348.6800000000001</v>
+        <v>356.2760000000001</v>
       </c>
       <c r="F82">
-        <v>607.6800000000001</v>
+        <v>615.2760000000001</v>
       </c>
       <c r="G82">
         <v>23.5</v>
@@ -8011,45 +8011,45 @@
         <v>71.875</v>
       </c>
       <c r="M82">
-        <v>89.20742400000002</v>
+        <v>123.5474208</v>
       </c>
       <c r="N82">
-        <v>-17.33242400000002</v>
+        <v>-51.67242080000001</v>
       </c>
       <c r="O82">
-        <v>-4.159781760000004</v>
+        <v>-12.401380992</v>
       </c>
       <c r="P82">
-        <v>-13.17264224000001</v>
+        <v>-39.27103980800001</v>
       </c>
       <c r="Q82">
-        <v>14.32735775999999</v>
+        <v>-11.77103980800001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2192386012626497</v>
+        <v>0.237351930250438</v>
       </c>
       <c r="T82">
-        <v>2.387447629534099</v>
+        <v>2.636784420998291</v>
       </c>
       <c r="U82">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1933695563275092</v>
+        <v>0.1396225019373289</v>
       </c>
       <c r="W82">
-        <v>0.1184133491311217</v>
+        <v>0.1727638016109843</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y82">
-        <v>0.805706484697955</v>
+        <v>0.5817604247388708</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1850355460524805</v>
+        <v>0.1865855460524805</v>
       </c>
       <c r="C83">
-        <v>-374.3574495195294</v>
+        <v>-384.3471523014833</v>
       </c>
       <c r="D83">
-        <v>217.4185504804707</v>
+        <v>215.0248476985168</v>
       </c>
       <c r="E83">
-        <v>356.2760000000001</v>
+        <v>363.8720000000001</v>
       </c>
       <c r="F83">
-        <v>615.2760000000001</v>
+        <v>622.8720000000001</v>
       </c>
       <c r="G83">
         <v>23.5</v>
@@ -8093,37 +8093,37 @@
         <v>71.875</v>
       </c>
       <c r="M83">
-        <v>123.5474208</v>
+        <v>125.0726976</v>
       </c>
       <c r="N83">
-        <v>-51.67242080000001</v>
+        <v>-53.19769760000001</v>
       </c>
       <c r="O83">
-        <v>-12.401380992</v>
+        <v>-12.767447424</v>
       </c>
       <c r="P83">
-        <v>-39.27103980800001</v>
+        <v>-40.43025017600001</v>
       </c>
       <c r="Q83">
-        <v>-11.77103980800001</v>
+        <v>-12.93025017600001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.237351930250438</v>
+        <v>0.24799370415324</v>
       </c>
       <c r="T83">
-        <v>2.636784420998291</v>
+        <v>2.783272444387084</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.1396225019373289</v>
+        <v>0.1379197884990689</v>
       </c>
       <c r="W83">
-        <v>0.1727638016109843</v>
+        <v>0.173105706469387</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.5817604247388708</v>
+        <v>0.574665785412787</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1865855460524805</v>
+        <v>0.1881355460524805</v>
       </c>
       <c r="C84">
-        <v>-384.3471523014833</v>
+        <v>-394.2847213836704</v>
       </c>
       <c r="D84">
-        <v>215.0248476985168</v>
+        <v>212.6832786163297</v>
       </c>
       <c r="E84">
-        <v>363.8720000000001</v>
+        <v>371.4680000000001</v>
       </c>
       <c r="F84">
-        <v>622.8720000000001</v>
+        <v>630.4680000000001</v>
       </c>
       <c r="G84">
         <v>23.5</v>
@@ -8175,37 +8175,37 @@
         <v>71.875</v>
       </c>
       <c r="M84">
-        <v>125.0726976</v>
+        <v>126.5979744</v>
       </c>
       <c r="N84">
-        <v>-53.19769760000001</v>
+        <v>-54.72297440000001</v>
       </c>
       <c r="O84">
-        <v>-12.767447424</v>
+        <v>-13.133513856</v>
       </c>
       <c r="P84">
-        <v>-40.43025017600001</v>
+        <v>-41.58946054400001</v>
       </c>
       <c r="Q84">
-        <v>-12.93025017600001</v>
+        <v>-14.08946054400001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.24799370415324</v>
+        <v>0.2598874514563718</v>
       </c>
       <c r="T84">
-        <v>2.783272444387084</v>
+        <v>2.946994352880443</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.1379197884990689</v>
+        <v>0.1362581043002849</v>
       </c>
       <c r="W84">
-        <v>0.173105706469387</v>
+        <v>0.1734393726565028</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.574665785412787</v>
+        <v>0.5677421012511872</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1881355460524805</v>
+        <v>0.1896855460524805</v>
       </c>
       <c r="C85">
-        <v>-394.2847213836704</v>
+        <v>-404.1718415892751</v>
       </c>
       <c r="D85">
-        <v>212.6832786163297</v>
+        <v>210.392158410725</v>
       </c>
       <c r="E85">
-        <v>371.4680000000001</v>
+        <v>379.0640000000001</v>
       </c>
       <c r="F85">
-        <v>630.4680000000001</v>
+        <v>638.0640000000001</v>
       </c>
       <c r="G85">
         <v>23.5</v>
@@ -8257,37 +8257,37 @@
         <v>71.875</v>
       </c>
       <c r="M85">
-        <v>126.5979744</v>
+        <v>128.1232512</v>
       </c>
       <c r="N85">
-        <v>-54.72297440000001</v>
+        <v>-56.24825120000003</v>
       </c>
       <c r="O85">
-        <v>-13.133513856</v>
+        <v>-13.49958028800001</v>
       </c>
       <c r="P85">
-        <v>-41.58946054400001</v>
+        <v>-42.74867091200002</v>
       </c>
       <c r="Q85">
-        <v>-14.08946054400001</v>
+        <v>-15.24867091200002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.2598874514563718</v>
+        <v>0.2732679171723951</v>
       </c>
       <c r="T85">
-        <v>2.946994352880443</v>
+        <v>3.131181499935471</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.1362581043002849</v>
+        <v>0.1346359840109958</v>
       </c>
       <c r="W85">
-        <v>0.1734393726565028</v>
+        <v>0.1737650944105921</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.5677421012511872</v>
+        <v>0.5609832667124824</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1896855460524805</v>
+        <v>0.1912355460524805</v>
       </c>
       <c r="C86">
-        <v>-404.171841589275</v>
+        <v>-414.0101259165119</v>
       </c>
       <c r="D86">
-        <v>210.392158410725</v>
+        <v>208.149874083488</v>
       </c>
       <c r="E86">
-        <v>379.064</v>
+        <v>386.66</v>
       </c>
       <c r="F86">
-        <v>638.064</v>
+        <v>645.66</v>
       </c>
       <c r="G86">
         <v>23.5</v>
@@ -8339,37 +8339,37 @@
         <v>71.875</v>
       </c>
       <c r="M86">
-        <v>128.1232512</v>
+        <v>129.648528</v>
       </c>
       <c r="N86">
-        <v>-56.2482512</v>
+        <v>-57.773528</v>
       </c>
       <c r="O86">
-        <v>-13.499580288</v>
+        <v>-13.86564672</v>
       </c>
       <c r="P86">
-        <v>-42.748670912</v>
+        <v>-43.90788128</v>
       </c>
       <c r="Q86">
-        <v>-15.248670912</v>
+        <v>-16.40788128</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.273267917172395</v>
+        <v>0.2884324449838879</v>
       </c>
       <c r="T86">
-        <v>3.131181499935469</v>
+        <v>3.3399269332645</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.1346359840109958</v>
+        <v>0.1330520312579253</v>
       </c>
       <c r="W86">
-        <v>0.173765094410592</v>
+        <v>0.1740831521234086</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.5609832667124826</v>
+        <v>0.5543834635746887</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1912355460524805</v>
+        <v>0.1927855460524805</v>
       </c>
       <c r="C87">
-        <v>-414.0101259165119</v>
+        <v>-423.8011193256885</v>
       </c>
       <c r="D87">
-        <v>208.149874083488</v>
+        <v>205.9548806743114</v>
       </c>
       <c r="E87">
-        <v>386.66</v>
+        <v>394.256</v>
       </c>
       <c r="F87">
-        <v>645.66</v>
+        <v>653.256</v>
       </c>
       <c r="G87">
         <v>23.5</v>
@@ -8421,37 +8421,37 @@
         <v>71.875</v>
       </c>
       <c r="M87">
-        <v>129.648528</v>
+        <v>131.1738048</v>
       </c>
       <c r="N87">
-        <v>-57.773528</v>
+        <v>-59.2988048</v>
       </c>
       <c r="O87">
-        <v>-13.86564672</v>
+        <v>-14.231713152</v>
       </c>
       <c r="P87">
-        <v>-43.90788128</v>
+        <v>-45.067091648</v>
       </c>
       <c r="Q87">
-        <v>-16.40788128</v>
+        <v>-17.567091648</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2884324449838879</v>
+        <v>0.3057633339113086</v>
       </c>
       <c r="T87">
-        <v>3.3399269332645</v>
+        <v>3.578493142783393</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.1330520312579253</v>
+        <v>0.1315049146153912</v>
       </c>
       <c r="W87">
-        <v>0.1740831521234086</v>
+        <v>0.1743938131452294</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.5543834635746887</v>
+        <v>0.547937144230797</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1927855460524805</v>
+        <v>0.1943355460524805</v>
       </c>
       <c r="C88">
-        <v>-423.8011193256885</v>
+        <v>-433.5463022891551</v>
       </c>
       <c r="D88">
-        <v>205.9548806743114</v>
+        <v>203.805697710845</v>
       </c>
       <c r="E88">
-        <v>394.256</v>
+        <v>401.852</v>
       </c>
       <c r="F88">
-        <v>653.256</v>
+        <v>660.852</v>
       </c>
       <c r="G88">
         <v>23.5</v>
@@ -8503,37 +8503,37 @@
         <v>71.875</v>
       </c>
       <c r="M88">
-        <v>131.1738048</v>
+        <v>132.6990816</v>
       </c>
       <c r="N88">
-        <v>-59.2988048</v>
+        <v>-60.8240816</v>
       </c>
       <c r="O88">
-        <v>-14.231713152</v>
+        <v>-14.597779584</v>
       </c>
       <c r="P88">
-        <v>-45.067091648</v>
+        <v>-46.226302016</v>
       </c>
       <c r="Q88">
-        <v>-17.567091648</v>
+        <v>-18.726302016</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.3057633339113086</v>
+        <v>0.3257605134429477</v>
       </c>
       <c r="T88">
-        <v>3.578493142783393</v>
+        <v>3.853761846074423</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1315049146153912</v>
+        <v>0.1299933638726856</v>
       </c>
       <c r="W88">
-        <v>0.1743938131452294</v>
+        <v>0.1746973325343648</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.547937144230797</v>
+        <v>0.54163901613619</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1943355460524805</v>
+        <v>0.1958855460524805</v>
       </c>
       <c r="C89">
-        <v>-433.5463022891551</v>
+        <v>-443.2470941212835</v>
       </c>
       <c r="D89">
-        <v>203.805697710845</v>
+        <v>201.7009058787165</v>
       </c>
       <c r="E89">
-        <v>401.852</v>
+        <v>409.448</v>
       </c>
       <c r="F89">
-        <v>660.852</v>
+        <v>668.448</v>
       </c>
       <c r="G89">
         <v>23.5</v>
@@ -8585,37 +8585,37 @@
         <v>71.875</v>
       </c>
       <c r="M89">
-        <v>132.6990816</v>
+        <v>134.2243584</v>
       </c>
       <c r="N89">
-        <v>-60.8240816</v>
+        <v>-62.3493584</v>
       </c>
       <c r="O89">
-        <v>-14.597779584</v>
+        <v>-14.963846016</v>
       </c>
       <c r="P89">
-        <v>-46.226302016</v>
+        <v>-47.385512384</v>
       </c>
       <c r="Q89">
-        <v>-18.726302016</v>
+        <v>-19.885512384</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3257605134429477</v>
+        <v>0.34909055622986</v>
       </c>
       <c r="T89">
-        <v>3.853761846074423</v>
+        <v>4.174908666580626</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1299933638726856</v>
+        <v>0.1285161665559506</v>
       </c>
       <c r="W89">
-        <v>0.1746973325343648</v>
+        <v>0.1749939537555651</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.54163901613619</v>
+        <v>0.5354840273164606</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1958855460524805</v>
+        <v>0.1974355460524805</v>
       </c>
       <c r="C90">
-        <v>-443.2470941212835</v>
+        <v>-452.9048561042147</v>
       </c>
       <c r="D90">
-        <v>201.7009058787165</v>
+        <v>199.6391438957853</v>
       </c>
       <c r="E90">
-        <v>409.448</v>
+        <v>417.044</v>
       </c>
       <c r="F90">
-        <v>668.448</v>
+        <v>676.044</v>
       </c>
       <c r="G90">
         <v>23.5</v>
@@ -8667,37 +8667,37 @@
         <v>71.875</v>
       </c>
       <c r="M90">
-        <v>134.2243584</v>
+        <v>135.7496352</v>
       </c>
       <c r="N90">
-        <v>-62.3493584</v>
+        <v>-63.8746352</v>
       </c>
       <c r="O90">
-        <v>-14.963846016</v>
+        <v>-15.329912448</v>
       </c>
       <c r="P90">
-        <v>-47.385512384</v>
+        <v>-48.544722752</v>
       </c>
       <c r="Q90">
-        <v>-19.885512384</v>
+        <v>-21.044722752</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.34909055622986</v>
+        <v>0.3766624249780291</v>
       </c>
       <c r="T90">
-        <v>4.174908666580626</v>
+        <v>4.554445818087956</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1285161665559506</v>
+        <v>0.1270721646845354</v>
       </c>
       <c r="W90">
-        <v>0.1749939537555651</v>
+        <v>0.1752839093313453</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5354840273164606</v>
+        <v>0.5294673528522307</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1974355460524805</v>
+        <v>0.1989855460524805</v>
       </c>
       <c r="C91">
-        <v>-452.9048561042147</v>
+        <v>-462.5208944238382</v>
       </c>
       <c r="D91">
-        <v>199.6391438957853</v>
+        <v>197.6191055761618</v>
       </c>
       <c r="E91">
-        <v>417.044</v>
+        <v>424.64</v>
       </c>
       <c r="F91">
-        <v>676.044</v>
+        <v>683.64</v>
       </c>
       <c r="G91">
         <v>23.5</v>
@@ -8749,37 +8749,37 @@
         <v>71.875</v>
       </c>
       <c r="M91">
-        <v>135.7496352</v>
+        <v>137.274912</v>
       </c>
       <c r="N91">
-        <v>-63.8746352</v>
+        <v>-65.399912</v>
       </c>
       <c r="O91">
-        <v>-15.329912448</v>
+        <v>-15.69597888</v>
       </c>
       <c r="P91">
-        <v>-48.544722752</v>
+        <v>-49.70393312</v>
       </c>
       <c r="Q91">
-        <v>-21.044722752</v>
+        <v>-22.20393312</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.3766624249780291</v>
+        <v>0.4097486674758321</v>
       </c>
       <c r="T91">
-        <v>4.554445818087956</v>
+        <v>5.009890399896752</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1270721646845354</v>
+        <v>0.1256602517435961</v>
       </c>
       <c r="W91">
-        <v>0.1752839093313453</v>
+        <v>0.1755674214498859</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5294673528522307</v>
+        <v>0.5235843822649837</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1989855460524805</v>
+        <v>0.2005355460524805</v>
       </c>
       <c r="C92">
-        <v>-462.5208944238382</v>
+        <v>-472.0964629293137</v>
       </c>
       <c r="D92">
-        <v>197.6191055761618</v>
+        <v>195.6395370706863</v>
       </c>
       <c r="E92">
-        <v>424.64</v>
+        <v>432.236</v>
       </c>
       <c r="F92">
-        <v>683.64</v>
+        <v>691.236</v>
       </c>
       <c r="G92">
         <v>23.5</v>
@@ -8831,37 +8831,37 @@
         <v>71.875</v>
       </c>
       <c r="M92">
-        <v>137.274912</v>
+        <v>138.8001888</v>
       </c>
       <c r="N92">
-        <v>-65.399912</v>
+        <v>-66.9251888</v>
       </c>
       <c r="O92">
-        <v>-15.69597888</v>
+        <v>-16.062045312</v>
       </c>
       <c r="P92">
-        <v>-49.70393312</v>
+        <v>-50.86314348800001</v>
       </c>
       <c r="Q92">
-        <v>-22.20393312</v>
+        <v>-23.36314348800001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4097486674758321</v>
+        <v>0.45018740830648</v>
       </c>
       <c r="T92">
-        <v>5.009890399896752</v>
+        <v>5.566544888774168</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1256602517435961</v>
+        <v>0.1242793698563038</v>
       </c>
       <c r="W92">
-        <v>0.1755674214498859</v>
+        <v>0.1758447025328542</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5235843822649837</v>
+        <v>0.5178307077345993</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2005355460524805</v>
+        <v>0.2020855460524805</v>
       </c>
       <c r="C93">
-        <v>-472.0964629293137</v>
+        <v>-481.6327657283823</v>
       </c>
       <c r="D93">
-        <v>195.6395370706863</v>
+        <v>193.6992342716178</v>
       </c>
       <c r="E93">
-        <v>432.236</v>
+        <v>439.8320000000001</v>
       </c>
       <c r="F93">
-        <v>691.236</v>
+        <v>698.8320000000001</v>
       </c>
       <c r="G93">
         <v>23.5</v>
@@ -8913,37 +8913,37 @@
         <v>71.875</v>
       </c>
       <c r="M93">
-        <v>138.8001888</v>
+        <v>140.3254656</v>
       </c>
       <c r="N93">
-        <v>-66.9251888</v>
+        <v>-68.45046560000003</v>
       </c>
       <c r="O93">
-        <v>-16.062045312</v>
+        <v>-16.42811174400001</v>
       </c>
       <c r="P93">
-        <v>-50.86314348800001</v>
+        <v>-52.02235385600002</v>
       </c>
       <c r="Q93">
-        <v>-23.36314348800001</v>
+        <v>-24.52235385600002</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.45018740830648</v>
+        <v>0.5007358343447902</v>
       </c>
       <c r="T93">
-        <v>5.566544888774168</v>
+        <v>6.262362999870942</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1242793698563038</v>
+        <v>0.1229285071404744</v>
       </c>
       <c r="W93">
-        <v>0.1758447025328542</v>
+        <v>0.1761159557661927</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5178307077345993</v>
+        <v>0.5122021130853101</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2020855460524805</v>
+        <v>0.2036355460524805</v>
       </c>
       <c r="C94">
-        <v>-481.6327657283823</v>
+        <v>-491.1309596297559</v>
       </c>
       <c r="D94">
-        <v>193.6992342716178</v>
+        <v>191.7970403702442</v>
       </c>
       <c r="E94">
-        <v>439.8320000000001</v>
+        <v>447.4280000000001</v>
       </c>
       <c r="F94">
-        <v>698.8320000000001</v>
+        <v>706.4280000000001</v>
       </c>
       <c r="G94">
         <v>23.5</v>
@@ -8995,37 +8995,37 @@
         <v>71.875</v>
       </c>
       <c r="M94">
-        <v>140.3254656</v>
+        <v>141.8507424</v>
       </c>
       <c r="N94">
-        <v>-68.45046560000003</v>
+        <v>-69.97574240000003</v>
       </c>
       <c r="O94">
-        <v>-16.42811174400001</v>
+        <v>-16.79417817600001</v>
       </c>
       <c r="P94">
-        <v>-52.02235385600002</v>
+        <v>-53.18156422400003</v>
       </c>
       <c r="Q94">
-        <v>-24.52235385600002</v>
+        <v>-25.68156422400003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5007358343447902</v>
+        <v>0.5657266678226175</v>
       </c>
       <c r="T94">
-        <v>6.262362999870942</v>
+        <v>7.156986285566792</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1229285071404744</v>
+        <v>0.1216066952357381</v>
       </c>
       <c r="W94">
-        <v>0.1761159557661927</v>
+        <v>0.1763813755966638</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5122021130853101</v>
+        <v>0.5066945634822422</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2036355460524805</v>
+        <v>0.2051855460524805</v>
       </c>
       <c r="C95">
-        <v>-491.1309596297559</v>
+        <v>-500.5921564429977</v>
       </c>
       <c r="D95">
-        <v>191.7970403702442</v>
+        <v>189.9318435570024</v>
       </c>
       <c r="E95">
-        <v>447.4280000000001</v>
+        <v>455.0240000000001</v>
       </c>
       <c r="F95">
-        <v>706.4280000000001</v>
+        <v>714.0240000000001</v>
       </c>
       <c r="G95">
         <v>23.5</v>
@@ -9077,37 +9077,37 @@
         <v>71.875</v>
       </c>
       <c r="M95">
-        <v>141.8507424</v>
+        <v>143.3760192</v>
       </c>
       <c r="N95">
-        <v>-69.97574240000003</v>
+        <v>-71.50101920000003</v>
       </c>
       <c r="O95">
-        <v>-16.79417817600001</v>
+        <v>-17.16024460800001</v>
       </c>
       <c r="P95">
-        <v>-53.18156422400003</v>
+        <v>-54.34077459200002</v>
       </c>
       <c r="Q95">
-        <v>-25.68156422400003</v>
+        <v>-26.84077459200002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.5657266678226175</v>
+        <v>0.6523811124597204</v>
       </c>
       <c r="T95">
-        <v>7.156986285566792</v>
+        <v>8.349817333161258</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1216066952357381</v>
+        <v>0.1203130069885494</v>
       </c>
       <c r="W95">
-        <v>0.1763813755966638</v>
+        <v>0.1766411481966993</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.5066945634822422</v>
+        <v>0.5013041957856226</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2051855460524805</v>
+        <v>0.2406744002832775</v>
       </c>
       <c r="C96">
-        <v>-500.5921564429977</v>
+        <v>-542.7769146379312</v>
       </c>
       <c r="D96">
-        <v>189.9318435570024</v>
+        <v>155.3430853620688</v>
       </c>
       <c r="E96">
-        <v>455.0240000000001</v>
+        <v>462.6200000000001</v>
       </c>
       <c r="F96">
-        <v>714.0240000000001</v>
+        <v>721.6200000000001</v>
       </c>
       <c r="G96">
         <v>23.5</v>
@@ -9159,45 +9159,45 @@
         <v>71.875</v>
       </c>
       <c r="M96">
-        <v>143.3760192</v>
+        <v>170.157996</v>
       </c>
       <c r="N96">
-        <v>-71.50101920000003</v>
+        <v>-98.28299600000003</v>
       </c>
       <c r="O96">
-        <v>-17.16024460800001</v>
+        <v>-23.58791904000001</v>
       </c>
       <c r="P96">
-        <v>-54.34077459200002</v>
+        <v>-74.69507696000002</v>
       </c>
       <c r="Q96">
-        <v>-26.84077459200002</v>
+        <v>-47.19507696000002</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.6523811124597204</v>
+        <v>0.7874744195676039</v>
       </c>
       <c r="T96">
-        <v>8.349817333161258</v>
+        <v>10.20942755529521</v>
       </c>
       <c r="U96">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.1203130069885494</v>
+        <v>0.101376370229466</v>
       </c>
       <c r="W96">
-        <v>0.1766411481966993</v>
+        <v>0.2118954518998919</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y96">
-        <v>0.5013041957856226</v>
+        <v>0.4224015426227751</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2406744002832775</v>
+        <v>0.2425744002832775</v>
       </c>
       <c r="C97">
-        <v>-542.7769146379312</v>
+        <v>-551.8728651485822</v>
       </c>
       <c r="D97">
-        <v>155.3430853620688</v>
+        <v>153.8431348514179</v>
       </c>
       <c r="E97">
-        <v>462.6200000000001</v>
+        <v>470.2160000000001</v>
       </c>
       <c r="F97">
-        <v>721.6200000000001</v>
+        <v>729.2160000000001</v>
       </c>
       <c r="G97">
         <v>23.5</v>
@@ -9241,37 +9241,37 @@
         <v>71.875</v>
       </c>
       <c r="M97">
-        <v>170.157996</v>
+        <v>171.9491328</v>
       </c>
       <c r="N97">
-        <v>-98.28299600000003</v>
+        <v>-100.0741328</v>
       </c>
       <c r="O97">
-        <v>-23.58791904000001</v>
+        <v>-24.01779187200001</v>
       </c>
       <c r="P97">
-        <v>-74.69507696000002</v>
+        <v>-76.05634092800003</v>
       </c>
       <c r="Q97">
-        <v>-47.19507696000002</v>
+        <v>-48.55634092800003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.7874744195676039</v>
+        <v>0.9728930244595053</v>
       </c>
       <c r="T97">
-        <v>10.20942755529521</v>
+        <v>12.76178444411902</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.101376370229466</v>
+        <v>0.1003203663729091</v>
       </c>
       <c r="W97">
-        <v>0.2118954518998919</v>
+        <v>0.212144457609268</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.4224015426227751</v>
+        <v>0.4180015265537879</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2425744002832775</v>
+        <v>0.2444744002832775</v>
       </c>
       <c r="C98">
-        <v>-551.8728651485822</v>
+        <v>-560.9401264474758</v>
       </c>
       <c r="D98">
-        <v>153.8431348514178</v>
+        <v>152.3718735525242</v>
       </c>
       <c r="E98">
-        <v>470.216</v>
+        <v>477.812</v>
       </c>
       <c r="F98">
-        <v>729.216</v>
+        <v>736.812</v>
       </c>
       <c r="G98">
         <v>23.5</v>
@@ -9323,37 +9323,37 @@
         <v>71.875</v>
       </c>
       <c r="M98">
-        <v>171.9491328</v>
+        <v>173.7402696</v>
       </c>
       <c r="N98">
-        <v>-100.0741328</v>
+        <v>-101.8652696</v>
       </c>
       <c r="O98">
-        <v>-24.017791872</v>
+        <v>-24.447664704</v>
       </c>
       <c r="P98">
-        <v>-76.056340928</v>
+        <v>-77.417604896</v>
       </c>
       <c r="Q98">
-        <v>-48.556340928</v>
+        <v>-49.917604896</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.9728930244595029</v>
+        <v>1.281924032612671</v>
       </c>
       <c r="T98">
-        <v>12.76178444411899</v>
+        <v>17.01571259215865</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.1003203663729091</v>
+        <v>0.09928613579174507</v>
       </c>
       <c r="W98">
-        <v>0.212144457609268</v>
+        <v>0.2123883291803065</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.4180015265537879</v>
+        <v>0.4136922324656045</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2444744002832775</v>
+        <v>0.2463744002832775</v>
       </c>
       <c r="C99">
-        <v>-560.9401264474758</v>
+        <v>-569.9795138356016</v>
       </c>
       <c r="D99">
-        <v>152.3718735525242</v>
+        <v>150.9284861643984</v>
       </c>
       <c r="E99">
-        <v>477.812</v>
+        <v>485.408</v>
       </c>
       <c r="F99">
-        <v>736.812</v>
+        <v>744.408</v>
       </c>
       <c r="G99">
         <v>23.5</v>
@@ -9405,37 +9405,37 @@
         <v>71.875</v>
       </c>
       <c r="M99">
-        <v>173.7402696</v>
+        <v>175.5314064</v>
       </c>
       <c r="N99">
-        <v>-101.8652696</v>
+        <v>-103.6564064</v>
       </c>
       <c r="O99">
-        <v>-24.447664704</v>
+        <v>-24.877537536</v>
       </c>
       <c r="P99">
-        <v>-77.417604896</v>
+        <v>-78.778868864</v>
       </c>
       <c r="Q99">
-        <v>-49.917604896</v>
+        <v>-51.278868864</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.281924032612671</v>
+        <v>1.899986048919006</v>
       </c>
       <c r="T99">
-        <v>17.01571259215865</v>
+        <v>25.52356888823798</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09928613579174507</v>
+        <v>0.09827301195713542</v>
       </c>
       <c r="W99">
-        <v>0.2123883291803065</v>
+        <v>0.2126272237805075</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.4136922324656045</v>
+        <v>0.409470883154731</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2463744002832775</v>
+        <v>0.2482744002832775</v>
       </c>
       <c r="C100">
-        <v>-569.9795138356016</v>
+        <v>-578.9918120111297</v>
       </c>
       <c r="D100">
-        <v>150.9284861643984</v>
+        <v>149.5121879888703</v>
       </c>
       <c r="E100">
-        <v>485.408</v>
+        <v>493.004</v>
       </c>
       <c r="F100">
-        <v>744.408</v>
+        <v>752.004</v>
       </c>
       <c r="G100">
         <v>23.5</v>
@@ -9487,37 +9487,37 @@
         <v>71.875</v>
       </c>
       <c r="M100">
-        <v>175.5314064</v>
+        <v>177.3225432</v>
       </c>
       <c r="N100">
-        <v>-103.6564064</v>
+        <v>-105.4475432</v>
       </c>
       <c r="O100">
-        <v>-24.877537536</v>
+        <v>-25.307410368</v>
       </c>
       <c r="P100">
-        <v>-78.778868864</v>
+        <v>-80.14013283200001</v>
       </c>
       <c r="Q100">
-        <v>-51.278868864</v>
+        <v>-52.64013283200001</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.899986048919006</v>
+        <v>3.754172097838012</v>
       </c>
       <c r="T100">
-        <v>25.52356888823798</v>
+        <v>51.04713777647596</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09827301195713542</v>
+        <v>0.09728035527069973</v>
       </c>
       <c r="W100">
-        <v>0.2126272237805075</v>
+        <v>0.212861292227169</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.409470883154731</v>
+        <v>0.4053348136279155</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2482744002832775</v>
-      </c>
-      <c r="C101">
-        <v>-578.9918120111297</v>
-      </c>
-      <c r="D101">
-        <v>149.5121879888703</v>
-      </c>
-      <c r="E101">
-        <v>493.004</v>
-      </c>
-      <c r="F101">
-        <v>752.004</v>
-      </c>
-      <c r="G101">
-        <v>23.5</v>
-      </c>
-      <c r="H101">
-        <v>500.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>99.375</v>
-      </c>
-      <c r="K101">
-        <v>27.5</v>
-      </c>
-      <c r="L101">
-        <v>71.875</v>
-      </c>
-      <c r="M101">
-        <v>177.3225432</v>
-      </c>
-      <c r="N101">
-        <v>-105.4475432</v>
-      </c>
-      <c r="O101">
-        <v>-25.307410368</v>
-      </c>
-      <c r="P101">
-        <v>-80.14013283200001</v>
-      </c>
-      <c r="Q101">
-        <v>-52.64013283200001</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>3.754172097838012</v>
-      </c>
-      <c r="T101">
-        <v>51.04713777647596</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09728035527069973</v>
-      </c>
-      <c r="W101">
-        <v>0.212861292227169</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.4053348136279155</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
